--- a/wp-snippets/plan/site-improvement-plan-20260906.xlsx
+++ b/wp-snippets/plan/site-improvement-plan-20260906.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スケジュール" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="委員会で決めること" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反映手順・技術メモ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公開の手順" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -549,22 +549,21 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>秋川流域花火大会 公式サイト 改善計画表（2026-09-06 更新）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
+          <t>第8回 秋川流域花火大会 公式サイト 改善計画表（2026年9月6日 更新）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>来場者目線の導線「知る → 行きたくなる → 自分に合った楽しみ方を見つける → チケットを購入する → 安心して当日を迎える」に沿って、メルマガ配信（9/17・10/8・10/22・10/31）と大会当日（11/14）から逆算しています。【9/6時点】第1弾（購入方法の整理・座席診断・写真の拡大・席カードの予約ボタン・読み上げ対応）は実装と検証が完了し、本番反映の承認待ちです。確認用の下書きページ: https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true （WordPressにログインした状態で開いてください）</t>
+          <t>来場者の目線「知る → 行きたくなる → 自分に合った楽しみ方を見つける → チケットを購入する → 安心して当日を迎える」に沿って施策を並べ、メールマガジンの配信（9/17・10/8・10/22・10/31）と大会当日（11/14）から逆算して日程を組んでいます。　【9月6日時点】第1弾（チケット入手方法の整理／座席診断／写真の拡大表示／席ごとの予約ボタン／読み上げ対応）は制作と点検が完了し、公開待ちの状態です。公開前の確認用ページ https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true （サイト管理画面にログインできる方のみ閲覧できます）　状況欄の色 … 緑：制作完了（公開待ち）／黄：対応・ご判断待ち／無色：これから着手</t>
         </is>
       </c>
     </row>
@@ -596,7 +595,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>実行委員会で用意・決めるもの</t>
+          <t>実行委員会で用意・決めていただくもの</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -611,7 +610,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>工数目安</t>
+          <t>作業量の目安</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -626,22 +625,17 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>連動するメルマガ・節目</t>
+          <t>連動するメールマガジン・節目</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>担当</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>データ根拠・備考</t>
+          <t>補足・データ根拠</t>
         </is>
       </c>
     </row>
@@ -653,27 +647,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>(即時対応)</t>
+          <t>（すぐ対応）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>旧URL /contact/inquiry/ の404をお問い合わせページへリダイレクト</t>
+          <t>見つからないページ（旧URL）をお問い合わせページへ転送する</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>直接流入で404が発生しており、問い合わせ機会を逃している</t>
+          <t>「ページが見つかりません」が表示され、お問い合わせの機会を逃している</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>リダイレクト設定(301)</t>
+          <t>転送設定を1件追加</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>旧URLが載っている媒体(チラシ・QR・メール)の確認</t>
+          <t>旧URLが載っている媒体（チラシ・QRコード・メール等）のご確認</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -706,19 +700,14 @@
           <t>―</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>萩原さん</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>萩原さん操作待ち</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>wp-admin →「リダイレクト」→ 元URL https://machizukuri-con.or.jp/contact/inquiry/ 、先URL https://machizukuri-con.or.jp/contact/ で追加。※設定変更はClaudeの自動モードでは実行できないため手動でお願いします。他の旧URL(*.html)は転送済みで問題なし</t>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>対応・ご判断待ち</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>サイト管理画面のリダイレクト設定に1件追加するだけで対応できます（旧URL → お問い合わせページ）。その他の旧URL（*.html）はすでに転送設定済みで問題ありません</t>
         </is>
       </c>
     </row>
@@ -730,7 +719,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>(即時対応)</t>
+          <t>（すぐ対応）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -745,7 +734,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>席の写真5枚・駐車場の案内図2枚・スクロール写真7枚の計14枚にWordPress標準の拡大表示を設定</t>
+          <t>席の写真5枚・駐車場の案内図2枚・横並び写真7枚の計14枚を、タップで拡大表示できるように設定</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -755,7 +744,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>デッドクリック率 16.7%→10%以下、クイックバック率 27%→20%以下</t>
+          <t>押しても反応しない箇所へのタップ 16.7%→10%以下、すぐ戻る割合 27%→20%以下</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -775,27 +764,22 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>承認後すぐ</t>
+          <t>公開待ち</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>9/17 第2回メルマガ前</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>サイト</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>実装済み・反映待ち</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>Clarity(8/29-9/4): デッドクリック253セッション、クイックバック411セッション。モバイル約85%。下書き4524で動作確認済み</t>
+          <t>9/17 第2回配信前</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>制作完了（公開待ち）</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>アクセス解析（8/29-9/4）: 反応しない箇所へのタップ253件、すぐ前のページに戻った操作411件。閲覧の約85%がスマートフォン。確認用ページで動作確認済み</t>
         </is>
       </c>
     </row>
@@ -822,7 +806,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>各カードに「アソビューで予約する」ボタン(既存と同じ形)と「他の販売サイトで購入する」リンクを追加</t>
+          <t>各席の紹介欄に「アソビューで予約する」ボタン（既存と同じ形）と「他の販売サイトで購入する」リンクを追加</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -832,7 +816,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>席カードからの予約クリック数</t>
+          <t>席の紹介欄からの予約クリック数</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -852,27 +836,22 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>承認後すぐ</t>
+          <t>公開待ち</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>9/17 第2回メルマガ前</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>サイト</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>実装済み・反映待ち</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>ベンチマーク由来のクイックフィックス1。アソビューの席種別URLは公開終了のため、一覧ページ(席を選んで進む案内つき)へリンク</t>
+          <t>9/17 第2回配信前</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>制作完了（公開待ち）</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>他大会サイトとの比較調査で挙がっていた改善点。アソビューの席種別ページは公開が終了しているため、席の一覧ページ（どの席を選ぶかの案内つき）へご案内しています</t>
         </is>
       </c>
     </row>
@@ -884,12 +863,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>(即時対応)</t>
+          <t>（すぐ対応）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>読み上げ・検索対応(写真の説明文、対応表の「〇」を文字に)</t>
+          <t>読み上げ・検索への対応（写真の説明文、対応表の記号を文字に）</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -899,7 +878,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>写真14枚とロゴ5枚に説明(alt)を付与、販売サイト対応表のアイコンを文字「〇」に置換</t>
+          <t>写真14枚と販売サイトのロゴ5枚に説明文を付与し、対応表の記号を文字に置き換え</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -909,7 +888,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>―(見た目は変わりません)</t>
+          <t>―（見た目は変わりません）</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -929,7 +908,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>承認後すぐ</t>
+          <t>公開待ち</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -937,19 +916,14 @@
           <t>―</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>サイト</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>実装済み・反映待ち</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>ベンチマーク由来のクイックフィックス2。対応表のアイコンは画像扱いで検索エンジンには空欄に見えていた</t>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>制作完了（公開待ち）</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>他大会サイトとの比較調査で挙がっていた改善点。販売サイト対応表の印は画像として扱われており、検索エンジンには空欄に見えていました</t>
         </is>
       </c>
     </row>
@@ -976,7 +950,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>チケットページ最上部に目的別3カード(今すぐ買う→一般販売/地域を応援→ふるさと納税/大会を応援→寄付・協賛)を設置</t>
+          <t>チケットページの最上部に、目的別の3つの入口（今すぐ購入→一般販売／地域を応援→ふるさと納税／大会を応援→寄付・協賛）を設置</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -986,7 +960,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>チケットページ→アソビュー予約クリック率、ふるさと納税・寄付ページへの遷移数</t>
+          <t>チケットページ→予約クリック率、ふるさと納税・寄付ページへの遷移数</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1006,27 +980,22 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>承認後すぐ</t>
+          <t>公開待ち</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>9/17 第2回メルマガ</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>サイト+委員会</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>実装済み・反映待ち</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>チケットページは28日で2,171PV(サイト2位)。アソビュー予約クリック316/週(+185%)と購入意欲が高い今が改善効果が最大</t>
+          <t>9/17 第2回配信</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>制作完了（公開待ち）</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>チケットページは28日間で2,171回閲覧（サイト内2位）。予約サイトへのクリックは週316回（前週比+185%）と関心が高まっている時期のため、改善の効果が出やすいタイミングです</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1022,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2〜3問の診断を実装。結果に席名・写真・価格・理由・予約ボタン・第2候補・「※おすすめは目安です」を表示。全20通り</t>
+          <t>2〜3問の診断を制作。結果に席名・写真・価格・おすすめの理由・予約ボタン・第2候補・「※おすすめは目安です」を表示（全20通り）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>おすすめの振り分け(20通り)の確認 ※「委員会で決めること」シート参照</t>
+          <t>おすすめの振り分け（20通り）のご確認　※「委員会で決めること」シートをご覧ください</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1083,27 +1052,22 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>承認後すぐ</t>
+          <t>公開待ち</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>9/17 第2回メルマガ「座席写真で席選び」と連動</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>サイト+委員会</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>実装済み・反映待ち</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>販売はA席369席に対しS席118・SS席46。目標達成率はS席131%、SS席92%、A席6.8%(9/4時点)。A席は20通り中15通りで画面に出る設計</t>
+          <t>9/17 第2回配信「座席写真で席選び」と連動</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>制作完了（公開待ち）</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>9月4日時点の販売はA席369席・S席118席・SS席46席。目標に対する達成率はS席131%、SS席92%に対しA席は6.8%。A席は20通りのうち15通りで画面に表示される組み立てにしています</t>
         </is>
       </c>
     </row>
@@ -1115,27 +1079,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>(反映作業)</t>
+          <t>（公開作業）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>本番のチケットページ(/ticket/)へ反映する</t>
+          <t>チケットページを公開する</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>0-2〜⑦をまとめて公開する</t>
+          <t>0-2〜⑦をまとめて公開します</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>下書き4524と同じ本文をチケットページに反映 → スマホ実機で表示確認 → 問題なければ完了(リビジョンで元に戻せます)</t>
+          <t>確認用ページと同じ内容をチケットページに反映 → スマートフォンの実機で表示を確認 → 問題なければ完了</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>反映してよいかの承認</t>
+          <t>公開してよいかのご判断</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1165,22 +1129,17 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>9/17 第2回メルマガ前</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>萩原さん→サイト</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>萩原さん操作待ち</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>手順は「反映手順・技術メモ」シート。Claudeの自動モードでは本番ページの書き換えが止まるため、承認をいただいてから実行します</t>
+          <t>9/17 第2回配信前</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>対応・ご判断待ち</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>手順は「公開の手順」シートをご覧ください。公開後も、サイトの変更履歴からいつでも元の状態に戻せます</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1151,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>(計測)</t>
+          <t>（計測）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>GA4に座席診断の項目を登録する</t>
+          <t>アクセス解析に座席診断の項目を登録する</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>診断の効果を数字で見られるようにする</t>
+          <t>診断の効果を数字で確認できるようにする</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>GA4 管理→カスタム定義で seat_type / quiz_with / quiz_priority / quiz_area / quiz_source を登録。seat_quiz_cta をキーイベントに</t>
+          <t>アクセス解析（GA4）に、選ばれた席・回答内容・予約ボタンのクリックを記録する設定を追加</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1232,7 +1191,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>反映と同時</t>
+          <t>公開と同時</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
@@ -1247,17 +1206,12 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>サイト</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>登録前のデータは後から見られないため、反映と同時に行う</t>
+          <t>登録前のデータはさかのぼって見られないため、公開と同時に設定します</t>
         </is>
       </c>
     </row>
@@ -1269,22 +1223,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>(後片付け)</t>
+          <t>（後片付け）</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>確認用の下書きページ(4524)を削除</t>
+          <t>確認用ページを削除する</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>管理画面に確認用ページを残さない</t>
+          <t>管理画面に確認用のページを残さない</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>反映と表示確認が終わったらゴミ箱へ</t>
+          <t>公開と表示確認が終わったら削除</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1309,7 +1263,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>反映後</t>
+          <t>公開後</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1324,17 +1278,12 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>サイト</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>下書きなので一般の方には見えていません</t>
+          <t>下書きのため、一般の方には表示されていません</t>
         </is>
       </c>
     </row>
@@ -1346,22 +1295,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>(計測)</t>
+          <t>（計測）</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>メルマガ本文リンクへのUTMパラメータ付与</t>
+          <t>メールマガジンのリンクに計測用の印を付ける</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>メルマガ経由の訪問と購入行動を正しく計測する</t>
+          <t>配信からの訪問と購入の動きを正しく計測する</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Brevoのリンクに utm_source=brevo&amp;utm_medium=email&amp;utm_campaign=第n回 を設定</t>
+          <t>配信システムのリンクに、どの配信から来たかが分かる印を付けます</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1371,7 +1320,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>GA4でメルマガ流入セッション数・予約クリック数が把握できる</t>
+          <t>配信からの訪問数・予約クリック数が正確に分かる</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1401,17 +1350,12 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>サイト</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>現状はsendibm3.comのreferral扱い(11セッション/週)で効果測定が不正確</t>
+          <t>現在は配信システムのドメインからの参照として集計され、効果を正確に測れていません（週11件）</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1382,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>提案書は作成済み(トップページ整理_提案書_20260906.md)。ギャラリー→コンセプト+特徴3カード→第8回の見どころ→チケット→お知らせ3件→…の順に再構成</t>
+          <t>提案書を作成済み。写真・動画 → コンセプトと特徴 → 第8回の見どころ → チケット → お知らせ3件 … の順に再構成します</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1448,7 +1392,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>トップのスクロール到達率(現状51%)、トップ→チケットページ遷移率、クイックバック率</t>
+          <t>トップページのスクロール到達率（現状51%）、トップ→チケットページ遷移率、すぐ戻る割合</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1473,22 +1417,17 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>10/8 第3回メルマガ前</t>
+          <t>10/8 第3回配信前</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>サイト+委員会</t>
+          <t>提案済み（素材待ち）</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>提案書あり・素材待ち</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>トップは28日で3,782PV・入口の73%。閲覧の65%が1ページで完了(Clarity)。お知らせ6件中2件が重複・1件が昨年の情報</t>
+          <t>トップページは28日間で3,782回閲覧、入口の73%。閲覧の65%が1ページだけで終了。現在お知らせ6件のうち2件が重複、1件は昨年の情報</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1464,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>セクション閲覧数、「秋川 紅葉」「サマーランド 花火」等の検索表示回数とCTR、平均滞在時間</t>
+          <t>該当箇所の閲覧数、「秋川 紅葉」「サマーランド 花火」等の検索表示回数とクリック率、平均滞在時間</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1550,22 +1489,17 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>10/8 第3回メルマガ「体験価値」に本文リンク</t>
+          <t>10/8 第3回配信「体験価値」に本文リンク</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>サイト+委員会</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>検索「サマーランド 花火」表示63/クリック22、「あきる野 花火」表示43/クリック11と地域検索に伸びしろ。周辺観光ページに18スポットの素材あり</t>
+          <t>検索「サマーランド 花火」は表示63回・クリック22回、「あきる野 花火」は表示43回・クリック11回で、地域名の検索に伸びしろがあります。周辺観光ページに18スポットの素材あり</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1536,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>セクション閲覧数、出店者募集ページとの回遊</t>
+          <t>該当箇所の閲覧数、出店者募集ページとの回遊</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1627,22 +1561,17 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>10/8 第3回メルマガ</t>
+          <t>10/8 第3回配信</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>サイト+委員会</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>出店者募集ページが28日で372PV(+75%)と関心が高い。アソビュー掲載文の「キッチンカー30台以上」も活用できる</t>
+          <t>出店者募集ページは28日間で372回閲覧（前月比+75%）と関心が高い項目です</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1608,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>ページ閲覧数、Instagramへの外部クリック数</t>
+          <t>ページ閲覧数、SNSへのクリック数</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1704,22 +1633,17 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>10/22 第4回メルマガ</t>
+          <t>10/22 第4回配信</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>サイト+委員会</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>Instagram流入は11セッション/週、X(t.co)5と小さく、サイト側からSNSへ送る導線も弱い</t>
+          <t>SNSからの訪問はInstagram週11件、X週5件と少なく、サイトからSNSへの案内も弱い状態です</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1680,12 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>閲覧数、当日ガイドPDFへの流入</t>
+          <t>閲覧数、当日ガイドの利用数</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>中(確定後は高)</t>
+          <t>中（確定後は高）</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1771,7 +1695,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>プログラム確定後(目標10/10)</t>
+          <t>プログラム確定後（目標10/10）</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1781,22 +1705,17 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>10/22 第4回メルマガ</t>
+          <t>10/22 第4回配信</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>委員会→サイト</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>現在サイトに載っている時間は第7回の記録(飲食12:00〜20:00、パフォーマンス13:30〜17:30頃)。第8回の確定が前提</t>
+          <t>現在サイトに掲載している時間は第7回の記録です（飲食12:00〜20:00、パフォーマンス13:30〜17:30頃）。第8回のプログラム確定が前提となります</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1752,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>ページ閲覧数、FAQ・アクセスページとの回遊、問い合わせ件数の減少</t>
+          <t>ページ閲覧数、よくある質問・交通アクセスページとの回遊、お問い合わせ件数の減少</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1858,22 +1777,17 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>10/22 第4回メルマガ「購入前確認」に本文リンク</t>
+          <t>10/22 第4回配信「購入前確認」に本文リンク</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>サイト+委員会</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>交通アクセス296PV・よくある質問313PV(28日)。アクセスページの「帰りの案内」は現在『確定次第公開』のまま</t>
+          <t>交通アクセス296回・よくある質問313回の閲覧（28日間）。アクセスページの帰りの案内は現在「確定次第公開」のままです</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1824,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>当日週のトップ閲覧数、開催情報ページ閲覧数、問い合わせ件数</t>
+          <t>当日週のトップページ閲覧数、開催情報ページ閲覧数、お問い合わせ件数</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1920,7 +1834,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>1日+当日運用</t>
+          <t>1日＋当日運用</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1935,22 +1849,17 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>10/31 第5回メルマガ、11/13〜14当日運用</t>
+          <t>10/31 第5回配信、11/13〜14 当日運用</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>委員会→サイト</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>FAQには「基本的に雨天決行」「11月は最高16℃・最低6℃」の記載あり。中止判断の基準・告知方法は未掲載。払い戻しは『イベント中止の場合のみ』</t>
+          <t>よくある質問には「基本的に雨天決行」「11月は最高16℃・最低6℃」の記載があります。中止判断の基準と告知方法は未掲載、払い戻しは「イベント中止の場合のみ」となっています</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1896,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>PDFダウンロード数(Clarityで計測、現状6セッション/週)</t>
+          <t>ダウンロード数（現状は週6件）</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2012,20 +1921,15 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>10/31 第5回メルマガに添付/リンク</t>
+          <t>10/31 第5回配信に添付・リンク</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>サイト+委員会</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>④⑧⑩の内容を流用して作成するため、それらの確定が前提</t>
         </is>
@@ -2033,7 +1937,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2066,7 +1970,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>週別スケジュール（✔=実装完了 ■=作業 ★=公開 ◆=節目）※9/6時点</t>
+          <t>週別スケジュール（✔=制作完了　■=作業　★=公開　◆=節目）　※2026年9月6日時点</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2049,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>節目(メルマガ・大会)</t>
+          <t>節目（メールマガジン・大会）</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr"/>
@@ -2188,7 +2092,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>404リダイレクト</t>
+          <t>旧URLの転送設定</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr"/>
@@ -2246,7 +2150,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SS/S/A席に予約ボタン</t>
+          <t>SS・S・A席に予約ボタン</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -2277,7 +2181,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>読み上げ・検索対応(alt等)</t>
+          <t>読み上げ・検索対応</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -2370,7 +2274,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>本番反映(承認→公開)</t>
+          <t>チケットページの公開</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr"/>
@@ -2397,7 +2301,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>GA4に診断の項目を登録</t>
+          <t>アクセス解析の設定</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -2424,7 +2328,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>確認用の下書きを削除</t>
+          <t>確認用ページの削除</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr"/>
@@ -2451,7 +2355,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>メルマガUTM付与</t>
+          <t>配信リンクの計測設定</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr"/>
@@ -2707,7 +2611,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>当日ガイドPDF</t>
+          <t>当日ガイド</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr"/>
@@ -2737,7 +2641,7 @@
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>※ 9/1週の「✔」は、9/5〜9/6に実装と検証まで完了したもの。9/8週の「★」は本番反映(公開)の予定です。</t>
+          <t>※ 9/1週の「✔」は制作と点検が完了したもの、9/8週の「★」は公開の予定です。</t>
         </is>
       </c>
     </row>
@@ -2752,28 +2656,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>実行委員会で用意・決めていただくもの（期限順）※9/6更新</t>
+          <t>実行委員会でご用意・ご判断いただきたいこと（期限順）　※2026年9月6日更新</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「座席診断の内容」は、いただいた事実の範囲で妥当な初期案として作ってあります（結果画面には必ず「※おすすめは目安です」と表示）。9/17のメルマガまでにご確認いただければ、修正は1行の書き換えで対応できます。</t>
+          <t>座席診断のおすすめ内容は、現在サイトに掲載されている情報の範囲で初期案として作成しています（結果画面には必ず「※おすすめは目安です」と表示しています）。9月17日の配信までにご確認いただければ、変更はすぐに反映できます。ご回答は右端の欄にご記入ください。</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2688,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>必要なもの・決めること</t>
+          <t>ご用意・ご判断いただきたいこと</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2795,17 +2698,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>今の扱い(仮置き)</t>
+          <t>現在の扱い（仮置き）</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>状況</t>
+          <t>ご回答・決定内容</t>
         </is>
       </c>
     </row>
@@ -2817,21 +2715,20 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>本番のチケットページへ反映してよいかの承認</t>
+          <t>チケットページを公開してよいかのご判断</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>★ 反映作業</t>
+          <t>★ 公開作業</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>下書き4524で確認できます。承認後すぐ反映できます</t>
+          <t>確認用ページでご覧いただけます。ご判断後すぐに公開できます</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2851,11 +2748,10 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>妥当な初期案として設定済み。結果に「※おすすめは目安です」を表示</t>
+          <t>初期案として設定済み。結果に「※おすすめは目安です」を表示</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2879,7 +2775,6 @@
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2903,7 +2798,6 @@
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2927,7 +2821,6 @@
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2951,7 +2844,6 @@
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2975,7 +2867,6 @@
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2999,7 +2890,6 @@
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3023,7 +2913,6 @@
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3033,21 +2922,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー写真・動画(横・縦)、キャッチコピー、今年の見どころ3点(写真つき)</t>
+          <t>トップページ用の写真・動画（横・縦）、キャッチコピー、今年の見どころ3点（写真つき）</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>① トップ整理</t>
+          <t>① トップページの整理</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>―(素材がないと着手できません)</t>
+          <t>―（素材がそろってからの着手となります）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3057,7 +2945,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>席種ごとの座席図(どのエリアか)。あれば診断の理由文に「花火の見え方」を書けます</t>
+          <t>席種ごとの配置が分かる図。いただければ「花火の見え方」を説明に加えられます</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3067,11 +2955,10 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>位置の情報がないため「指定席で場所取り不要」を軸に説明</t>
+          <t>配置の情報がないため「指定席で場所取りが不要」という点を中心に説明</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3081,7 +2968,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>予約ボタンの色をサイト全体でそろえるか(診断は少し暗い赤#d40000、既存ボタンは#ff0000)</t>
+          <t>予約ボタンの色をサイト全体でそろえるか（座席診断は文字の読みやすさの基準を満たす少し暗い赤、既存ボタンは従来の赤）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3091,11 +2978,10 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>診断だけ読みやすさ基準を満たす暗めの赤。他は既存のまま</t>
+          <t>座席診断のみ暗めの赤。ほかは従来どおり</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3119,7 +3005,6 @@
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3143,7 +3028,6 @@
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3167,7 +3051,6 @@
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3191,7 +3074,6 @@
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3215,7 +3097,6 @@
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3239,7 +3120,6 @@
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3263,7 +3143,6 @@
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3287,7 +3166,6 @@
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3307,15 +3185,14 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>そのまま表示。連絡をいただければ振り分けを1行変更します</t>
+          <t>そのまま表示しています。ご連絡いただければ、おすすめする席を変更します</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3340,7 +3217,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>効果指標の基準値（2026/8/29〜9/4に取得）と目標</t>
+          <t>効果を測る指標　現状値（2026年8月29日〜9月4日）と目標</t>
         </is>
       </c>
     </row>
@@ -3352,44 +3229,44 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>基準値(9/5取得)</t>
+          <t>現状値（9月上旬）</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>目標(目安)</t>
+          <t>目標（目安）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>計測ツール</t>
+          <t>確認方法</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>関連施策</t>
+          <t>関係する施策</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>週間訪問者数 / ページビュー</t>
+          <t>週間の訪問者数 / 閲覧数</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1,340人 / 3,930PV(前週比+101%/+110%)</t>
+          <t>1,340人 / 3,930回（前週比 +101% / +110%）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>メルマガ配信週で2,000人以上</t>
+          <t>配信のある週で2,000人以上</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>WP Statistics</t>
+          <t>サイト内のアクセス集計</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3401,22 +3278,22 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>検索クリック数 / CTR / 平均掲載順位(週)</t>
+          <t>検索からのクリック数 / クリック率 / 平均掲載順位（週）</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>648 / 14.4% / 5.6位</t>
+          <t>648回 / 14.4% / 5.6位</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CTR 16%以上(地域検索の改善)</t>
+          <t>クリック率16%以上（地域名の検索の改善）</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Search Console</t>
+          <t>検索エンジンの管理ツール</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -3428,22 +3305,22 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>チケットページ閲覧数(28日)</t>
+          <t>チケットページの閲覧数（28日間）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2,171PV</t>
+          <t>2,171回</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>3,000PV</t>
+          <t>3,000回</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>GA4</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3455,22 +3332,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>アソビュー予約クリック数(週)</t>
+          <t>予約サイトへのクリック数（週）</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>316回(前週比+185%)</t>
+          <t>316回（前週比 +185%）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>メルマガ配信週で400回以上</t>
+          <t>配信のある週で400回以上</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>GA4 ticket_click_asoview</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -3482,7 +3359,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>トップページのスクロール到達率</t>
+          <t>トップページを下まで読んだ割合</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -3497,7 +3374,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>行動分析ツール</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3509,12 +3386,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>クイックバック率(すぐ戻る)</t>
+          <t>開いてすぐ前のページに戻った割合</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>27%(411セッション)</t>
+          <t>27%（411件）</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3524,7 +3401,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>行動分析ツール</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -3536,12 +3413,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>デッドクリック率</t>
+          <t>押しても反応しない箇所へのタップ</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>16.7%(253セッション)</t>
+          <t>16.7%（253件）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3551,7 +3428,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>行動分析ツール</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3563,7 +3440,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>新規ユーザー比率</t>
+          <t>初めて訪れた方の割合</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -3573,12 +3450,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>―(参考)</t>
+          <t>―（参考値）</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>行動分析ツール</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -3590,22 +3467,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>メルマガ経由セッション(週)</t>
+          <t>メールマガジン経由の訪問（週）</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>11(referral扱い)</t>
+          <t>11件（正確に計測できていない状態）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>UTMで正確に計測→開封数の20%以上</t>
+          <t>計測を整えたうえで、開封数の20%以上</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>GA4</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -3617,22 +3494,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>PDFダウンロード(週)</t>
+          <t>資料のダウンロード数（週）</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6セッション</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>大会前週に300以上</t>
+          <t>大会前週に300件以上</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>行動分析ツール</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3644,12 +3521,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>404発生</t>
+          <t>「ページが見つかりません」の発生</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>/contact/inquiry/ で発生中</t>
+          <t>旧URLで発生中</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3659,7 +3536,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>WP Statistics</t>
+          <t>サイト内のアクセス集計</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -3671,12 +3548,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>チケット販売(累計・9/4時点)</t>
+          <t>チケット販売（累計・9月4日時点）</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>882席 / 5,518,000円(目標比20.5%)</t>
+          <t>882席 / 5,518,000円（目標比 20.5%）</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3698,22 +3575,22 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>【新】座席診断の開始数(週)</t>
+          <t>【新】座席診断を始めた数（週）</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>未計測(反映後に取得)</t>
+          <t>未計測（公開後に取得）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>反映後1週間の実測値をもとに設定</t>
+          <t>公開後1週間の実測をもとに設定</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>GA4 seat_quiz_start</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3725,7 +3602,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>【新】座席診断の結果表示数(週)</t>
+          <t>【新】診断結果まで進んだ数（週）</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -3735,12 +3612,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>開始数の80%以上(途中離脱が少ない)</t>
+          <t>始めた数の80%以上（途中でやめる方が少ない）</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>GA4 seat_quiz_result</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -3752,7 +3629,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>【新】診断→予約ボタンのタップ率</t>
+          <t>【新】診断結果から予約ボタンを押した割合</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -3767,7 +3644,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>GA4 seat_quiz_cta ÷ seat_quiz_result</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -3789,12 +3666,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>A席の予約が増えているか(現状A席は目標比6.8%)</t>
+          <t>A席の予約が増えているか（現状A席は目標比6.8%）</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>GA4 seat_type</t>
+          <t>アクセス解析</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -3816,12 +3693,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>デッドクリック率の低下で確認</t>
+          <t>反応しない箇所へのタップの減少で確認</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>行動分析ツール</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -3844,14 +3721,14 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>本番反映の手順と、作業上の注意（2026-09-06）</t>
+          <t>チケットページ公開までの手順と補足（2026年9月6日）</t>
         </is>
       </c>
     </row>
@@ -3875,67 +3752,67 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true （下書き。WordPressにログインした状態で開いてください。スマホでも確認できます）</t>
+          <t>https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true　（公開前の下書きです。サイト管理画面にログインできる方のみ閲覧できます。スマートフォンでもご確認いただけます）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>反映の手順①</t>
+          <t>手順①　ご判断</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>萩原さんから「反映して」とご連絡いただく（本番ページの書き換えは、Claudeの自動モードでは安全装置により止まるため）</t>
+          <t>確認用ページをご覧いただき、この内容で公開してよいかご判断ください</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>反映の手順②</t>
+          <t>手順②　公開</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>チケットページ(固定ページ「チケット情報」)の本文を、下書き4524と同じ内容に置き換える。※Claudeが実行できない場合は、エディタで下書き4524の全ブロックをコピー→チケット情報に貼り付け→更新でも同じ結果になります</t>
+          <t>チケットページ（固定ページ「チケット情報」）の内容を、確認用ページと同じ内容に差し替えます</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>反映の手順③</t>
+          <t>手順③　表示確認</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://machizukuri-con.or.jp/ticket/ をスマホ実機で開いて確認：上から「チケットの入手方法は3つ」→「どの席にしようか迷ったら」→「販売サイト」の順に並ぶ／診断が動く／写真をタップすると拡大する／横スクロールが出ない</t>
+          <t>公開後、https://machizukuri-con.or.jp/ticket/ をスマートフォンの実機で開いて確認します。確認する点：上から「チケットの入手方法は3つ」→「どの席にしようか迷ったら」→「販売サイト」の順に並ぶ／座席診断が動く／写真をタップすると拡大する／横にはみ出さない</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>反映の手順④</t>
+          <t>手順④　計測設定</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>GA4 管理→カスタム定義で seat_type / quiz_with / quiz_priority / quiz_area / quiz_source を登録（登録前のデータは後から見られません）</t>
+          <t>アクセス解析（GA4）に座席診断の項目を登録します。登録前のデータはさかのぼって見られないため、公開と同時に行います</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>反映の手順⑤</t>
+          <t>手順⑤　後片付け</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>確認用の下書き4524をゴミ箱へ</t>
+          <t>確認用の下書きページを削除します</t>
         </is>
       </c>
     </row>
@@ -3947,55 +3824,55 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>WordPressの「リビジョン」で1つ前に戻せます。反映前の本文もバックアップ済み（GitHub akigawa-hanabi / wp-snippets）</t>
+          <t>サイトの変更履歴から、いつでも公開前の状態に戻せます。公開前の内容も別途保管しています</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>⚠ サーバーの制約</t>
+          <t>変更していないもの</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ConoHa WING のセキュリティ機能(WAF)により、本文の先頭付近に JavaScript や CSSのコメント(/* */)があると保存が拒否されます（403エラー）。このため座席診断のプログラムは自前の配信先(akigawa-hanabi.pages.dev)から読み込む形にしています。今後もWordPress本文にプログラムを直接書くことはできません</t>
+          <t>既存の文言・価格・掲載していない項目は一切変更していません（変更部分以外が元の内容と完全に一致することを機械的に確認済みです）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>変更していないもの</t>
+          <t>座席診断の仕組みについて</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>既存の文言・価格・非表示ブロックは一切変更していません（元に戻す検証で、変更部分以外が元の本文と完全一致することを確認済み）</t>
+          <t>利用しているレンタルサーバーのセキュリティ機能により、ページ本文の中にプログラムを直接書き込むことができません。そのため座席診断のプログラムは、当会が管理する別の配信先から読み込む形にしています（表示・動作に違いはありません）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>資料の場所</t>
+          <t>確認した内容</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>OneDrive\ドキュメント\花火大会_作業ファイル\サイト改善\ に、まとめ（チケットページ改善_まとめ_20260906.md）、トップページ整理の提案書、座席診断の仕様書、新しい本文HTMLを保存しています</t>
+          <t>複数の案を比較したうえで制作し、事実関係・日本語表現・スマートフォン表示・動作・サイトへの組み込み・読み上げ対応の6つの観点で点検しました。パソコンとスマートフォンの表示、座席診断の全20通り、写真の拡大表示、編集画面でエラーが出ないことを実機で確認しています</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>検証の内容</t>
+          <t>関連資料</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3案を設計→2名で審査→実装→6つの観点(事実・日本語・スマホ表示・プログラム・WordPress互換・読み上げ対応)で2回検証し、指摘を反映済み。実ブラウザでPC/スマホ幅の表示、診断20通り、写真の拡大、エディタで「無効なブロック」が出ないことを確認</t>
+          <t>「チケットページ改善のまとめ」「トップページ整理の提案書」「座席診断の仕様書」を別途作成しています（ご入用の場合はお知らせください）</t>
         </is>
       </c>
     </row>

--- a/wp-snippets/plan/site-improvement-plan-20260906.xlsx
+++ b/wp-snippets/plan/site-improvement-plan-20260906.xlsx
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -130,6 +130,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -534,23 +537,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -563,7 +567,7 @@
     <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>来場者の目線「知る → 行きたくなる → 自分に合った楽しみ方を見つける → チケットを購入する → 安心して当日を迎える」に沿って施策を並べ、メールマガジンの配信（9/17・10/8・10/22・10/31）と大会当日（11/14）から逆算して日程を組んでいます。　【9月6日時点】第1弾（チケット入手方法の整理／座席診断／写真の拡大表示／席ごとの予約ボタン／読み上げ対応）は制作と点検が完了し、公開待ちの状態です。公開前の確認用ページ https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true （サイト管理画面にログインできる方のみ閲覧できます）　状況欄の色 … 緑：制作完了（公開待ち）／黄：対応・ご判断待ち／無色：これから着手</t>
+          <t>来場者の目線「知る → 行きたくなる → 自分に合った楽しみ方を見つける → チケットを購入する → 安心して当日を迎える」に沿って施策を並べ、メールマガジンの配信（9/17・10/8・10/22・10/31）と大会当日（11/14）から逆算して日程を組んでいます。　【9月6日時点】第1弾（チケット入手方法の整理／座席診断／写真の拡大表示／席ごとの予約ボタン／読み上げ対応）は制作と点検が完了し、公開待ちの状態です。公開前の確認用ページ https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true （サイト管理画面にログインできる方のみ閲覧できます）　状況欄の色 … 緑：制作完了（公開待ち）／黄：対応・ご判断待ち／無色：これから着手　「改善案の番号」欄は、ご提案いただいた改善案①〜⑩に対応しています（「追加」＝アクセス解析から見つかった課題、「作業」＝公開・計測などの作業）。No.は公開予定日の順の通し番号です。</t>
         </is>
       </c>
     </row>
@@ -575,1361 +579,1420 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>改善案の番号</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>導線の段階</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>施策</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>ねらい・期待効果</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>主な作業(サイト側)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>実行委員会で用意・決めていただくもの</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>効果指標(KPI)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>作業量の目安</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>着手</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>公開目標</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>連動するメールマガジン・節目</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>状況</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>補足・データ根拠</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
+      <c r="A5" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
           <t>（すぐ対応）</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>見つからないページ（旧URL）をお問い合わせページへ転送する</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>「ページが見つかりません」が表示され、お問い合わせの機会を逃している</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>転送設定を1件追加</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>旧URLが載っている媒体（チラシ・QRコード・メール等）のご確認</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>404アクセス 0件</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>5分</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>9/8</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>9/8</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>対応・ご判断待ち</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>サイト管理画面のリダイレクト設定に1件追加するだけで対応できます（旧URL → お問い合わせページ）。その他の旧URL（*.html）はすでに転送設定済みで問題ありません</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
+      <c r="A6" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
           <t>（すぐ対応）</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>チケットページの写真をタップで拡大できるようにする</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>「写真をタップしても何も起きない」で離脱する行動を減らす</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>席の写真5枚・駐車場の案内図2枚・横並び写真7枚の計14枚を、タップで拡大表示できるように設定</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>押しても反応しない箇所へのタップ 16.7%→10%以下、すぐ戻る割合 27%→20%以下</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>公開待ち</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>9/17 第2回配信前</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>アクセス解析（8/29-9/4）: 反応しない箇所へのタップ253件、すぐ前のページに戻った操作411件。閲覧の約85%がスマートフォン。確認用ページで動作確認済み</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>0-3</t>
-        </is>
+      <c r="A7" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>チケットを選ぶ・購入する</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>SS席・S席・A席のカードに予約ボタンを追加</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>席の説明を見たその場で購入に進めるようにする(従来はリクライニングとフリーエリアにしかボタンが無かった)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>各席の紹介欄に「アソビューで予約する」ボタン（既存と同じ形）と「他の販売サイトで購入する」リンクを追加</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>席の紹介欄からの予約クリック数</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>公開待ち</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>9/17 第2回配信前</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>他大会サイトとの比較調査で挙がっていた改善点。アソビューの席種別ページは公開が終了しているため、席の一覧ページ（どの席を選ぶかの案内つき）へご案内しています</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>0-4</t>
-        </is>
+      <c r="A8" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
           <t>（すぐ対応）</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>読み上げ・検索への対応（写真の説明文、対応表の記号を文字に）</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>音声読み上げでも席と販売サイトが分かるようにする。検索エンジンにも中身が伝わる</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>写真14枚と販売サイトのロゴ5枚に説明文を付与し、対応表の記号を文字に置き換え</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>写真の説明文の言い回し確認</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>―（見た目は変わりません）</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>公開待ち</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="N8" s="8" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>他大会サイトとの比較調査で挙がっていた改善点。販売サイト対応表の印は画像として扱われており、検索エンジンには空欄に見えていました</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>チケットを選ぶ・購入する</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>チケット入手方法の整理「あなたに合った購入方法」</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>一般販売/ふるさと納税/寄付・協賛の違いを目的から選べるようにし、迷いをなくす</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>チケットページの最上部に、目的別の3つの入口（今すぐ購入→一般販売／地域を応援→ふるさと納税／大会を応援→寄付・協賛）を設置</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>ふるさと納税の返礼品ページの受付期限、寄付・協賛の記載内容に変更がないか</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>チケットページ→予約クリック率、ふるさと納税・寄付ページへの遷移数</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>公開待ち</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>9/17 第2回配信</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="N9" s="8" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>チケットページは28日間で2,171回閲覧（サイト内2位）。予約サイトへのクリックは週316回（前週比+185%）と関心が高まっている時期のため、改善の効果が出やすいタイミングです</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>⑦</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>自分に合った楽しみ方を見つける</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>座席診断(どなたと→何を重視→おすすめ席→購入ボタン)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>初めての人が「席を調べて選ぶ」のではなく「教えてもらう」ことで購入まで進みやすくする</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>2〜3問の診断を制作。結果に席名・写真・価格・おすすめの理由・予約ボタン・第2候補・「※おすすめは目安です」を表示（全20通り）</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>おすすめの振り分け（20通り）のご確認　※「委員会で決めること」シートをご覧ください</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>診断の開始数・結果表示数、診断→予約クリック率、席種別の販売バランス</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>公開待ち</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>9/17 第2回配信「座席写真で席選び」と連動</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>9月4日時点の販売はA席369席・S席118席・SS席46席。目標に対する達成率はS席131%、SS席92%に対しA席は6.8%。A席は20通りのうち15通りで画面に表示される組み立てにしています</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
+      <c r="A11" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>作業</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
           <t>（公開作業）</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>チケットページを公開する</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>0-2〜⑦をまとめて公開します</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>確認用ページと同じ内容をチケットページに反映 → スマートフォンの実機で表示を確認 → 問題なければ完了</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>公開してよいかのご判断</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>10分</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>承認後</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>9/8</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>9/17 第2回配信前</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>対応・ご判断待ち</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>手順は「公開の手順」シートをご覧ください。公開後も、サイトの変更履歴からいつでも元の状態に戻せます</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
+      <c r="A12" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>作業</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
           <t>（計測）</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>アクセス解析に座席診断の項目を登録する</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>診断の効果を数字で確認できるようにする</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>アクセス解析（GA4）に、選ばれた席・回答内容・予約ボタンのクリックを記録する設定を追加</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>診断の開始数・結果表示数・予約タップ率</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>20分</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>公開と同時</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>9/8</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>登録前のデータはさかのぼって見られないため、公開と同時に設定します</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
+      <c r="A13" s="4" t="n">
+        <v>9</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
+          <t>作業</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
           <t>（後片付け）</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>確認用ページを削除する</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>管理画面に確認用のページを残さない</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>公開と表示確認が終わったら削除</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>5分</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>公開後</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>下書きのため、一般の方には表示されていません</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
+      <c r="A14" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>作業</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
           <t>（計測）</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>メールマガジンのリンクに計測用の印を付ける</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>配信からの訪問と購入の動きを正しく計測する</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>配信システムのリンクに、どの配信から来たかが分かる印を付けます</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>配信からの訪問数・予約クリック数が正確に分かる</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>各配信前30分</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>9/16</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>各配信前</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>9/17以降の全配信</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>現在は配信システムのドメインからの参照として集計され、効果を正確に測れていません（週11件）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>トップページの情報整理(写真・動画→コンセプト→今年の見どころ→チケット導線)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>詰め込みすぎを解消し、最初の画面で魅力が伝わる構成にする</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>提案書を作成済み。写真・動画 → コンセプトと特徴 → 第8回の見どころ → チケット → お知らせ3件 … の順に再構成します</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>ヒーロー写真・動画、キャッチコピー、今年の見どころ3点(写真つき)</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>トップページのスクロール到達率（現状51%）、トップ→チケットページ遷移率、すぐ戻る割合</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>3日</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>素材到着後</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>10/8 第3回配信前</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>提案済み（素材待ち）</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>トップページは28日間で3,782回閲覧、入口の73%。閲覧の65%が1ページだけで終了。現在お知らせ6件のうち2件が重複、1件は昨年の情報</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>「東京から約60分、紅葉・秋川渓谷・花火の秋の日帰り旅」の体験価値とモデルコース</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>都心の花火大会との差別化。昼:観光・紅葉→夕方:会場イベント→夜:音楽×花火という目的の複数化で来場動機を作る</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>トップまたは専用ページに「秋川で過ごす一日」セクションを作成。既存の周辺観光ページ(18スポット)と相互リンク</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>モデルコースに載せる観光スポットの選定、所要時間の目安、写真</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>該当箇所の閲覧数、「秋川 紅葉」「サマーランド 花火」等の検索表示回数とクリック率、平均滞在時間</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>9/29</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>10/3</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>10/8 第3回配信「体験価値」に本文リンク</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>検索「サマーランド 花火」は表示63回・クリック22回、「あきる野 花火」は表示43回・クリック11回で、地域名の検索に伸びしろがあります。周辺観光ページに18スポットの素材あり</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>飲食・ステージのアピール(食べる/見る/楽しむ/感動する)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>「花火直前に行くイベント」から「昼から楽しむイベント」へ認識を変える</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>4つの体験(キッチンカー・飲食ブース/ダンス・ステージ/秋川の自然・紅葉/音楽×花火)をカード形式で掲載</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>出店者・ステージ出演者の確定リスト、昨年の飲食・ステージ写真</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>該当箇所の閲覧数、出店者募集ページとの回遊</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>9/29</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>10/3</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>10/8 第3回配信</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>出店者募集ページは28日間で372回閲覧（前月比+75%）と関心が高い項目です</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>知る</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>SNS・メディア出演情報のまとめ「秋川流域花火大会をもっと知る」</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>購入前に雰囲気を知れる場所を作り、点在する情報を一箇所に集める</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Instagram埋め込み・メディア掲載一覧・過去の動画をまとめる。既存のメディア掲載ページを第8回向けに更新</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>掲載するInstagram投稿の選定、メディア掲載一覧(媒体名・日付・リンク)</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>ページ閲覧数、SNSへのクリック数</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>低〜中</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>1日</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>10/6</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>10/22 第4回配信</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>SNSからの訪問はInstagram週11件、X週5件と少なく、サイトからSNSへの案内も弱い状態です</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>行きたくなる</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>当日タイムスケジュールの掲載</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>「何時に行けばどう楽しめるか」を示し、昼からの来場を促す</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>開場〜終了までの時間軸を図で掲載(トップ・チケット・初めての方へページから参照)</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>開場時刻、ステージ進行、飲食開始時刻、花火打上時刻、終了時刻の確定</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>閲覧数、当日ガイドの利用数</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>中（確定後は高）</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>0.5日</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>プログラム確定後（目標10/10）</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>10/17</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>10/22 第4回配信</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>現在サイトに掲載している時間は第7回の記録です（飲食12:00〜20:00、パフォーマンス13:30〜17:30頃）。第8回のプログラム確定が前提となります</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>⑧</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>安心して当日を迎える</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>「初めて来る人へ」ページ(行く前/会場内/帰り)</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>アクセス・FAQに分散した情報を来場の時系列でまとめ、不安をなくす</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>到着推奨時刻、秋川駅からの行き方、電車/バス/車の比較、駐車場、会場マップ、帰りのバス時刻・注意点を1ページに構成</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>会場マップ最新版、トイレ・救護所・飲食ブースの位置、帰りのバス時刻、到着推奨時刻</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>ページ閲覧数、よくある質問・交通アクセスページとの回遊、お問い合わせ件数の減少</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>10/13</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>10/17</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>10/22 第4回配信「購入前確認」に本文リンク</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>交通アクセス296回・よくある質問313回の閲覧（28日間）。アクセスページの帰りの案内は現在「確定次第公開」のままです</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>⑩</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>安心して当日を迎える</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>天候・開催情報(開催/中止判断、雨天対応、服装・防寒、当日の天気)</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>当日の判断と準備の情報を一箇所で示し、電話問い合わせを減らす</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>トップ最上部に「開催情報」帯を用意(通常時は非表示)、専用ページに雨天時の対応・払い戻し・服装目安を掲載</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>中止判断のタイミングと告知ルール、荒天時の払い戻し方針、当日の更新担当者</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>当日週のトップページ閲覧数、開催情報ページ閲覧数、お問い合わせ件数</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>1日＋当日運用</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>10/20</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>10/24</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>10/31 第5回配信、11/13〜14 当日運用</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>よくある質問には「基本的に雨天決行」「11月は最高16℃・最低6℃」の記載があります。中止判断の基準と告知方法は未掲載、払い戻しは「イベント中止の場合のみ」となっています</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>⑨</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>安心して当日を迎える</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>当日ガイドPDF(会場MAP・タイムスケジュール・バス時刻表)</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>会場で電波がつながりにくくても困らないよう、事前に保存・印刷できる資料を配る</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>A4×1〜2枚のPDFを作成し、⑧ページ・購入完了後の案内・最終メルマガからダウンロードできるようにする</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>最終版の会場マップ、確定タイムスケジュール、バス時刻表</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>ダウンロード数（現状は週6件）</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>10/20</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>10/30</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>10/31 第5回配信に添付・リンク</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>④⑧⑩の内容を流用して作成するため、それらの確定が前提</t>
         </is>
@@ -1937,7 +2000,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1968,9 +2031,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>週別スケジュール（✔=制作完了　■=作業　★=公開　◆=節目）　※2026年9月6日時点</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>週別スケジュール（✔=制作完了　■=作業　★=公開　◆=節目）　※2026年9月6日時点。No.は「計画表」シートと同じ通し番号です</t>
         </is>
       </c>
     </row>
@@ -2042,604 +2105,568 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>節目（メールマガジン・大会）</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr"/>
-      <c r="D4" s="11" t="inlineStr"/>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>9/17 第2回配信</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr"/>
-      <c r="G4" s="11" t="inlineStr"/>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="12" t="inlineStr"/>
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>10/8 第3回配信</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr"/>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>10/22 第4回配信</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>10/31 第5回配信・販売最終</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr"/>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr"/>
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>11/14 大会当日</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>旧URLの転送設定</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr"/>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr"/>
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr"/>
-      <c r="H5" s="13" t="inlineStr"/>
-      <c r="I5" s="13" t="inlineStr"/>
-      <c r="J5" s="13" t="inlineStr"/>
-      <c r="K5" s="13" t="inlineStr"/>
-      <c r="L5" s="13" t="inlineStr"/>
-      <c r="M5" s="13" t="inlineStr"/>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr"/>
+      <c r="I5" s="14" t="inlineStr"/>
+      <c r="J5" s="14" t="inlineStr"/>
+      <c r="K5" s="14" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>写真をタップで拡大</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr"/>
-      <c r="F6" s="13" t="inlineStr"/>
-      <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr"/>
-      <c r="I6" s="13" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr"/>
-      <c r="K6" s="13" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr"/>
-      <c r="M6" s="13" t="inlineStr"/>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr"/>
+      <c r="J6" s="14" t="inlineStr"/>
+      <c r="K6" s="14" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>0-3</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>SS・S・A席に予約ボタン</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="13" t="inlineStr"/>
-      <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr"/>
-      <c r="I7" s="13" t="inlineStr"/>
-      <c r="J7" s="13" t="inlineStr"/>
-      <c r="K7" s="13" t="inlineStr"/>
-      <c r="L7" s="13" t="inlineStr"/>
-      <c r="M7" s="13" t="inlineStr"/>
+      <c r="E7" s="14" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
+      <c r="J7" s="14" t="inlineStr"/>
+      <c r="K7" s="14" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>0-4</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>読み上げ・検索対応</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr"/>
-      <c r="G8" s="13" t="inlineStr"/>
-      <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
-      <c r="J8" s="13" t="inlineStr"/>
-      <c r="K8" s="13" t="inlineStr"/>
-      <c r="L8" s="13" t="inlineStr"/>
-      <c r="M8" s="13" t="inlineStr"/>
+      <c r="E8" s="14" t="inlineStr"/>
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr"/>
+      <c r="J8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>⑥</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>チケット入手方法の整理</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="13" t="inlineStr"/>
-      <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="13" t="inlineStr"/>
-      <c r="I9" s="13" t="inlineStr"/>
-      <c r="J9" s="13" t="inlineStr"/>
-      <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr"/>
-      <c r="M9" s="13" t="inlineStr"/>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="14" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>⑦</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>座席診断</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="13" t="inlineStr"/>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
-      <c r="J10" s="13" t="inlineStr"/>
-      <c r="K10" s="13" t="inlineStr"/>
-      <c r="L10" s="13" t="inlineStr"/>
-      <c r="M10" s="13" t="inlineStr"/>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr"/>
+      <c r="J10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="inlineStr"/>
+      <c r="L10" s="14" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>チケットページの公開</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>チケットページの公開</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="14" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>アクセス解析の設定</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr"/>
-      <c r="F11" s="13" t="inlineStr"/>
-      <c r="G11" s="13" t="inlineStr"/>
-      <c r="H11" s="13" t="inlineStr"/>
-      <c r="I11" s="13" t="inlineStr"/>
-      <c r="J11" s="13" t="inlineStr"/>
-      <c r="K11" s="13" t="inlineStr"/>
-      <c r="L11" s="13" t="inlineStr"/>
-      <c r="M11" s="13" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>アクセス解析の設定</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr"/>
+      <c r="J12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>確認用ページの削除</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="14" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr"/>
-      <c r="F12" s="13" t="inlineStr"/>
-      <c r="G12" s="13" t="inlineStr"/>
-      <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
-      <c r="J12" s="13" t="inlineStr"/>
-      <c r="K12" s="13" t="inlineStr"/>
-      <c r="L12" s="13" t="inlineStr"/>
-      <c r="M12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>確認用ページの削除</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr"/>
-      <c r="D13" s="13" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>配信リンクの計測設定</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr"/>
-      <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="13" t="inlineStr"/>
-      <c r="J13" s="13" t="inlineStr"/>
-      <c r="K13" s="13" t="inlineStr"/>
-      <c r="L13" s="13" t="inlineStr"/>
-      <c r="M13" s="13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>配信リンクの計測設定</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr"/>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr"/>
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr"/>
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr"/>
-      <c r="K14" s="14" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="L14" s="13" t="inlineStr"/>
-      <c r="M14" s="13" t="inlineStr"/>
+      <c r="L14" s="14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>トップページの情報整理</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr"/>
-      <c r="D15" s="13" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr"/>
+      <c r="D15" s="14" t="inlineStr"/>
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>(素材待ち)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr"/>
-      <c r="I15" s="13" t="inlineStr"/>
-      <c r="J15" s="13" t="inlineStr"/>
-      <c r="K15" s="13" t="inlineStr"/>
-      <c r="L15" s="13" t="inlineStr"/>
-      <c r="M15" s="13" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr"/>
+      <c r="J15" s="14" t="inlineStr"/>
+      <c r="K15" s="14" t="inlineStr"/>
+      <c r="L15" s="14" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>体験価値・モデルコース</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr"/>
-      <c r="D16" s="13" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr"/>
-      <c r="J16" s="13" t="inlineStr"/>
-      <c r="K16" s="13" t="inlineStr"/>
-      <c r="L16" s="13" t="inlineStr"/>
-      <c r="M16" s="13" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr"/>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="14" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>飲食・ステージのアピール</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr"/>
-      <c r="D17" s="13" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr"/>
-      <c r="F17" s="13" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr"/>
+      <c r="D17" s="14" t="inlineStr"/>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="13" t="inlineStr"/>
-      <c r="K17" s="13" t="inlineStr"/>
-      <c r="L17" s="13" t="inlineStr"/>
-      <c r="M17" s="13" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="14" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>SNS・メディアまとめ</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr"/>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr"/>
-      <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr"/>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="inlineStr"/>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr"/>
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr"/>
-      <c r="J18" s="13" t="inlineStr"/>
-      <c r="K18" s="13" t="inlineStr"/>
-      <c r="L18" s="13" t="inlineStr"/>
-      <c r="M18" s="13" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr"/>
+      <c r="J18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="14" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>当日タイムスケジュール</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr"/>
-      <c r="D19" s="13" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr"/>
-      <c r="F19" s="13" t="inlineStr"/>
-      <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr"/>
+      <c r="D19" s="14" t="inlineStr"/>
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>(確定待ち)</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr"/>
-      <c r="K19" s="13" t="inlineStr"/>
-      <c r="L19" s="13" t="inlineStr"/>
-      <c r="M19" s="13" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="14" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>⑧</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>初めて来る人へ</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr"/>
-      <c r="D20" s="13" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr"/>
-      <c r="F20" s="13" t="inlineStr"/>
-      <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="14" t="inlineStr"/>
+      <c r="F20" s="14" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr"/>
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr"/>
-      <c r="K20" s="13" t="inlineStr"/>
-      <c r="L20" s="13" t="inlineStr"/>
-      <c r="M20" s="13" t="inlineStr"/>
+      <c r="J20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="inlineStr"/>
+      <c r="L20" s="14" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>⑩</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>天候・開催情報</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr"/>
-      <c r="D21" s="13" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="13" t="inlineStr"/>
-      <c r="G21" s="13" t="inlineStr"/>
-      <c r="H21" s="13" t="inlineStr"/>
-      <c r="I21" s="13" t="inlineStr"/>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr"/>
+      <c r="D21" s="14" t="inlineStr"/>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr"/>
+      <c r="J21" s="15" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="K21" s="13" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="17" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="M21" s="17" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>⑨</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>当日ガイド</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr"/>
-      <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="13" t="inlineStr"/>
-      <c r="G22" s="13" t="inlineStr"/>
-      <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr"/>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr"/>
+      <c r="I22" s="14" t="inlineStr"/>
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="K22" s="14" t="inlineStr">
+      <c r="K22" s="15" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="L22" s="13" t="inlineStr"/>
-      <c r="M22" s="16" t="inlineStr">
+      <c r="L22" s="14" t="inlineStr"/>
+      <c r="M22" s="17" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>※ 9/1週の「✔」は制作と点検が完了したもの、9/8週の「★」は公開の予定です。</t>
         </is>
@@ -2667,7 +2694,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>実行委員会でご用意・ご判断いただきたいこと（期限順）　※2026年9月6日更新</t>
         </is>
@@ -2708,487 +2735,487 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>9/8</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>チケットページを公開してよいかのご判断</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>★ 公開作業</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>No.7 チケットページの公開</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>確認用ページでご覧いただけます。ご判断後すぐに公開できます</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>座席診断のおすすめ振り分け(全20通り)の確認。特に「カップル×花火に集中＝S席」「おひとり×ゆったり＝A席」「おひとり×特別な時間＝S席」</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>No.6 座席診断</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>初期案として設定済み。結果に「※おすすめは目安です」を表示</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>A席「子ども2,000円」の年齢区分(何歳から席が必要か)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>No.6 座席診断</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>年齢は書かず「小さなお子さまの膝上観覧は無料です」のみ</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>フリーエリア「西多摩在住」の確認方法(全員が在住である必要があるか、証明は必要か)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>No.6 座席診断</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>「西多摩にお住まいの方だけが買える」までにとどめている</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>5名以上の家族・グループへの案内(SS席を2テーブル買えるか、隣同士になるか)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>No.6 座席診断</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>サイトに記載がないため書いていない</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>1人あたり換算(SS席8,750円/S席7,000円)と差額(A席→S席 あと4,000円)の表示可否</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>No.6 座席診断</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>表示価格の割り算・引き算のみで「〜の計算です」と記載</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>写真の説明文(alt)の言い回し 例:「SS席(4名掛けのテーブル席)の写真」</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>0-4 読み上げ対応</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>No.4 読み上げ・検索への対応</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>実際の画像を見て、席名と写っているものだけで記載</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>寄付・協賛カードの金額表記「寄付1万円から/中口協賛3万円から/大口協賛10万円以上」</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>⑥ 購入方法の整理</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>No.5 チケット入手方法の整理</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>寄付・協賛ページの記載どおり。特典の中身は書いていない</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>ふるさと納税の受付期限、返礼品ページのURLに変更がないか</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>⑥ 購入方法の整理</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>No.5 チケット入手方法の整理</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>現在のさとふるの返礼品一覧へリンク</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>トップページ用の写真・動画（横・縦）、キャッチコピー、今年の見どころ3点（写真つき）</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>① トップページの整理</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>No.11 トップページの整理</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>―（素材がそろってからの着手となります）</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>席種ごとの配置が分かる図。いただければ「花火の見え方」を説明に加えられます</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断 / ⑧ 初めて来る人へ</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>No.6 座席診断／No.16 初めて来る人へ</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>配置の情報がないため「指定席で場所取りが不要」という点を中心に説明</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>予約ボタンの色をサイト全体でそろえるか（座席診断は文字の読みやすさの基準を満たす少し暗い赤、既存ボタンは従来の赤）</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>0-3 / ⑦</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>No.3 予約ボタン／No.6 座席診断</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>座席診断のみ暗めの赤。ほかは従来どおり</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>モデルコースに載せる観光スポットの選定、所要時間の目安、写真</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>② 体験価値</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>No.12 体験価値・モデルコース</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>周辺観光ページの18スポットから選べます</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>出店者・ステージ出演者の確定リスト、昨年の飲食・ステージ写真</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>③ 飲食・ステージ</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>No.13 飲食・ステージ</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>未確定分は「予定」表記で先行公開も可能</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>10/3</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>掲載するInstagram投稿の選定、メディア掲載一覧(媒体・日付・リンク)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>⑤ SNS・メディアまとめ</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>No.14 SNS・メディアまとめ</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>第8回の当日プログラム(開場・ステージ進行・飲食開始・打上・終了時刻)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>④ タイムスケジュール / ⑨ 当日ガイド / ⑦の理由文</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>No.15 タイムスケジュール／No.18 当日ガイド／No.6 座席診断</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>サイトの時間は第7回の記録のまま(飲食12:00〜20:00等)</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>会場マップ最新版(座席・トイレ・救護所・飲食・ステージ)、到着推奨時刻</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>⑧ 初めて来る人へ / ⑨ 当日ガイド</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>No.16 初めて来る人へ／No.18 当日ガイド</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>帰りのバス時刻表(交通事業者へ確認)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>⑧ 初めて来る人へ / ⑨ 当日ガイド</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>No.16 初めて来る人へ／No.18 当日ガイド</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>アクセスページは「確定次第、順次公開します」のまま</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>10/17</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>中止判断のタイミングと告知ルール、荒天時の払い戻し方針、当日の更新担当者</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>⑩ 天候・開催情報</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>No.17 天候・開催情報</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>FAQは「基本的に雨天決行」「払い戻しはイベント中止の場合のみ」</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>10/24</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>会場マップ・タイムスケジュール・バス時刻表の最終版</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>⑨ 当日ガイドPDF</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>No.18 当日ガイド</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>随時</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>S席の追加販売が終わったとき/フリーエリアが完売したときの連絡</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 座席診断</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>No.6 座席診断</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>そのまま表示しています。ご連絡いただければ、おすすめする席を変更します</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3215,7 +3242,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>効果を測る指標　現状値（2026年8月29日〜9月4日）と目標</t>
         </is>
@@ -3249,461 +3276,461 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>週間の訪問者数 / 閲覧数</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>1,340人 / 3,930回（前週比 +101% / +110%）</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>配信のある週で2,000人以上</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>サイト内のアクセス集計</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>検索からのクリック数 / クリック率 / 平均掲載順位（週）</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>648回 / 14.4% / 5.6位</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>クリック率16%以上（地域名の検索の改善）</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>検索エンジンの管理ツール</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>①②</t>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>No.11・12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>チケットページの閲覧数（28日間）</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2,171回</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>3,000回</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>⑥⑦</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>No.5・6</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>予約サイトへのクリック数（週）</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>316回（前週比 +185%）</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>配信のある週で400回以上</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>⑥⑦0-3</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>No.3・5・6</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>トップページを下まで読んだ割合</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>60%以上</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>No.11</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>開いてすぐ前のページに戻った割合</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>27%（411件）</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>20%以下</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>0-2 ① ⑥</t>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>No.2・5・11</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>押しても反応しない箇所へのタップ</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>16.7%（253件）</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>10%以下</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>0-2</t>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>No.2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>初めて訪れた方の割合</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>77.7%</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>―（参考値）</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>メールマガジン経由の訪問（週）</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>11件（正確に計測できていない状態）</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>計測を整えたうえで、開封数の20%以上</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>+</t>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>No.10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>資料のダウンロード数（週）</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>6件</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>大会前週に300件以上</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>⑨</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>No.18</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>「ページが見つかりません」の発生</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>旧URLで発生中</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>0件</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>サイト内のアクセス集計</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>0-1</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>No.1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>チケット販売（累計・9月4日時点）</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>882席 / 5,518,000円（目標比 20.5%）</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>26,860,000円</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>売上集計シート</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>【新】座席診断を始めた数（週）</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>未計測（公開後に取得）</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>公開後1週間の実測をもとに設定</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>⑦</t>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>【新】診断結果まで進んだ数（週）</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>始めた数の80%以上（途中でやめる方が少ない）</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>⑦</t>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>【新】診断結果から予約ボタンを押した割合</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>30%以上</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>⑦</t>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>【新】診断でおすすめされた席の内訳</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>A席の予約が増えているか（現状A席は目標比6.8%）</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>⑦</t>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>【新】写真の拡大表示の利用</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>反応しない箇所へのタップの減少で確認</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>0-2</t>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>No.2</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3753,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>チケットページ公開までの手順と補足（2026年9月6日）</t>
         </is>
@@ -3745,132 +3772,132 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>確認用ページ</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true　（公開前の下書きです。サイト管理画面にログインできる方のみ閲覧できます。スマートフォンでもご確認いただけます）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>手順①　ご判断</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>確認用ページをご覧いただき、この内容で公開してよいかご判断ください</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>手順②　公開</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>チケットページ（固定ページ「チケット情報」）の内容を、確認用ページと同じ内容に差し替えます</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>手順③　表示確認</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>公開後、https://machizukuri-con.or.jp/ticket/ をスマートフォンの実機で開いて確認します。確認する点：上から「チケットの入手方法は3つ」→「どの席にしようか迷ったら」→「販売サイト」の順に並ぶ／座席診断が動く／写真をタップすると拡大する／横にはみ出さない</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>手順④　計測設定</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>アクセス解析（GA4）に座席診断の項目を登録します。登録前のデータはさかのぼって見られないため、公開と同時に行います</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>手順⑤　後片付け</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>確認用の下書きページを削除します</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>元に戻す方法</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>サイトの変更履歴から、いつでも公開前の状態に戻せます。公開前の内容も別途保管しています</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>変更していないもの</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>既存の文言・価格・掲載していない項目は一切変更していません（変更部分以外が元の内容と完全に一致することを機械的に確認済みです）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>座席診断の仕組みについて</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>利用しているレンタルサーバーのセキュリティ機能により、ページ本文の中にプログラムを直接書き込むことができません。そのため座席診断のプログラムは、当会が管理する別の配信先から読み込む形にしています（表示・動作に違いはありません）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>確認した内容</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>複数の案を比較したうえで制作し、事実関係・日本語表現・スマートフォン表示・動作・サイトへの組み込み・読み上げ対応の6つの観点で点検しました。パソコンとスマートフォンの表示、座席診断の全20通り、写真の拡大表示、編集画面でエラーが出ないことを実機で確認しています</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>関連資料</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>「チケットページ改善のまとめ」「トップページ整理の提案書」「座席診断の仕様書」を別途作成しています（ご入用の場合はお知らせください）</t>
         </is>

--- a/wp-snippets/plan/site-improvement-plan-20260906.xlsx
+++ b/wp-snippets/plan/site-improvement-plan-20260906.xlsx
@@ -48,7 +48,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
@@ -77,7 +82,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -132,7 +142,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -140,35 +153,41 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -542,19 +561,19 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,7 +586,7 @@
     <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>来場者の目線「知る → 行きたくなる → 自分に合った楽しみ方を見つける → チケットを購入する → 安心して当日を迎える」に沿って施策を並べ、メールマガジンの配信（9/17・10/8・10/22・10/31）と大会当日（11/14）から逆算して日程を組んでいます。　【9月6日時点】第1弾（チケット入手方法の整理／座席診断／写真の拡大表示／席ごとの予約ボタン／読み上げ対応）は制作と点検が完了し、公開待ちの状態です。公開前の確認用ページ https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true （サイト管理画面にログインできる方のみ閲覧できます）　状況欄の色 … 緑：制作完了（公開待ち）／黄：対応・ご判断待ち／無色：これから着手　「改善案の番号」欄は、ご提案いただいた改善案①〜⑩に対応しています（「追加」＝アクセス解析から見つかった課題、「作業」＝公開・計測などの作業）。No.は公開予定日の順の通し番号です。</t>
+          <t>来場者の目線「知る → 行きたくなる → 自分に合った楽しみ方を見つける → チケットを購入する → 安心して当日を迎える」に沿って施策を並べ、メールマガジンの配信（9/17・10/8・10/22・10/31）と大会当日（11/14）から逆算して日程を組んでいます。　【9月6日時点】第1弾（チケット入手方法の整理／座席診断／写真の拡大表示／席ごとの予約ボタン／読み上げ対応）は制作と点検が完了し、公開待ちの状態です。公開前の確認用ページ https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true （サイト管理画面にログインできる方のみ閲覧できます）　状況欄の色 … 緑：制作完了（公開待ち）／黄：対応・ご判断待ち／無色：これから着手　区分 … 「改善案」＝ご提案いただいた改善案（番号欄に①〜⑩を記載）／「追加改善」＝アクセス解析から新たに見つかった課題／「公開・計測」＝公開作業と効果測定の準備。　No.は公開予定日の順に並べた通し番号です。</t>
         </is>
       </c>
     </row>
@@ -579,62 +598,62 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>改善案の番号</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>導線の段階</t>
-        </is>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>来場者の段階</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>施策</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>ねらい・期待効果</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>主な作業(サイト側)</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>実行委員会で用意・決めていただくもの</t>
+          <t>主な作業（サイト側）</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>効果指標(KPI)</t>
+          <t>実行委員会でご用意・ご判断いただくこと</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>効果の見方（指標）</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>作業量の目安</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>着手</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>公開目標</t>
+          <t>予定（着手→公開）</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>連動するメールマガジン・節目</t>
+          <t>連動する配信・節目</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -652,72 +671,72 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>追加</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>（すぐ対応）</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>追加改善</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>サイト全体</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>見つからないページ（旧URL）をお問い合わせページへ転送する</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>「ページが見つかりません」が表示され、お問い合わせの機会を逃している</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>転送設定を1件追加</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>旧URLが載っている媒体（チラシ・QRコード・メール等）のご確認</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>404アクセス 0件</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>5分</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>9/8</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>9/8</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>9/8 に設定</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>対応・ご判断待ち</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>サイト管理画面のリダイレクト設定に1件追加するだけで対応できます（旧URL → お問い合わせページ）。その他の旧URL（*.html）はすでに転送設定済みで問題ありません</t>
         </is>
@@ -727,72 +746,72 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>追加</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>（すぐ対応）</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>追加改善</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>チケットを選ぶ・購入する</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>チケットページの写真をタップで拡大できるようにする</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>「写真をタップしても何も起きない」で離脱する行動を減らす</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>席の写真5枚・駐車場の案内図2枚・横並び写真7枚の計14枚を、タップで拡大表示できるように設定</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>押しても反応しない箇所へのタップ 16.7%→10%以下、すぐ戻る割合 27%→20%以下</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>9/5</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>公開待ち</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>0.5日</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>制作 9/5 → 公開待ち</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>9/17 第2回配信前</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>アクセス解析（8/29-9/4）: 反応しない箇所へのタップ253件、すぐ前のページに戻った操作411件。閲覧の約85%がスマートフォン。確認用ページで動作確認済み</t>
         </is>
@@ -802,72 +821,72 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>追加</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>追加改善</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>チケットを選ぶ・購入する</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>SS席・S席・A席のカードに予約ボタンを追加</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>SS席・S席・A席の紹介欄に予約ボタンを追加</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>席の説明を見たその場で購入に進めるようにする(従来はリクライニングとフリーエリアにしかボタンが無かった)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>各席の紹介欄に「アソビューで予約する」ボタン（既存と同じ形）と「他の販売サイトで購入する」リンクを追加</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>席の紹介欄からの予約クリック数</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>9/5</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>公開待ち</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>0.5日</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>制作 9/5 → 公開待ち</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>9/17 第2回配信前</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>他大会サイトとの比較調査で挙がっていた改善点。アソビューの席種別ページは公開が終了しているため、席の一覧ページ（どの席を選ぶかの案内つき）へご案内しています</t>
         </is>
@@ -877,72 +896,72 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>追加</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>（すぐ対応）</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>追加改善</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>サイト全体</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>読み上げ・検索への対応（写真の説明文、対応表の記号を文字に）</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>音声読み上げでも席と販売サイトが分かるようにする。検索エンジンにも中身が伝わる</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>写真14枚と販売サイトのロゴ5枚に説明文を付与し、対応表の記号を文字に置き換え</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>写真の説明文の言い回し確認</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>―（見た目は変わりません）</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>9/5</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>公開待ち</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>0.5日</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>制作 9/5 → 公開待ち</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>他大会サイトとの比較調査で挙がっていた改善点。販売サイト対応表の印は画像として扱われており、検索エンジンには空欄に見えていました</t>
         </is>
@@ -952,72 +971,72 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>チケットを選ぶ・購入する</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>チケット入手方法の整理「あなたに合った購入方法」</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>一般販売/ふるさと納税/寄付・協賛の違いを目的から選べるようにし、迷いをなくす</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>チケットページの最上部に、目的別の3つの入口（今すぐ購入→一般販売／地域を応援→ふるさと納税／大会を応援→寄付・協賛）を設置</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>ふるさと納税の返礼品ページの受付期限、寄付・協賛の記載内容に変更がないか</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>チケットページ→予約クリック率、ふるさと納税・寄付ページへの遷移数</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>9/5</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>公開待ち</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>1日</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>制作 9/5 → 公開待ち</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>9/17 第2回配信</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>チケットページは28日間で2,171回閲覧（サイト内2位）。予約サイトへのクリックは週316回（前週比+185%）と関心が高まっている時期のため、改善の効果が出やすいタイミングです</t>
         </is>
@@ -1027,72 +1046,72 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>⑦</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>自分に合った楽しみ方を見つける</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>座席診断(どなたと→何を重視→おすすめ席→購入ボタン)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>座席診断（2〜3問に答えると、おすすめの席がわかる）</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>初めての人が「席を調べて選ぶ」のではなく「教えてもらう」ことで購入まで進みやすくする</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>2〜3問の診断を制作。結果に席名・写真・価格・おすすめの理由・予約ボタン・第2候補・「※おすすめは目安です」を表示（全20通り）</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>おすすめの振り分け（20通り）のご確認　※「委員会で決めること」シートをご覧ください</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>診断の開始数・結果表示数、診断→予約クリック率、席種別の販売バランス</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>9/5</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>公開待ち</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>制作 9/5 → 公開待ち</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>9/17 第2回配信「座席写真で席選び」と連動</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>制作完了（公開待ち）</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>9月4日時点の販売はA席369席・S席118席・SS席46席。目標に対する達成率はS席131%、SS席92%に対しA席は6.8%。A席は20通りのうち15通りで画面に表示される組み立てにしています</t>
         </is>
@@ -1102,72 +1121,72 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>作業</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>（公開作業）</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>公開・計測</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>チケットページを公開する</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>0-2〜⑦をまとめて公開します</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>確認用ページと同じ内容をチケットページに反映 → スマートフォンの実機で表示を確認 → 問題なければ完了</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>公開してよいかのご判断</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>10分</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>承認後</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>9/8</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>ご判断後すぐ（目標 9/8）</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>9/17 第2回配信前</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="8" t="inlineStr">
         <is>
           <t>対応・ご判断待ち</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>手順は「公開の手順」シートをご覧ください。公開後も、サイトの変更履歴からいつでも元の状態に戻せます</t>
         </is>
@@ -1177,72 +1196,72 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>作業</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>（計測）</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>公開・計測</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>アクセス解析に座席診断の項目を登録する</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>診断の効果を数字で確認できるようにする</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>アクセス解析（GA4）に、選ばれた席・回答内容・予約ボタンのクリックを記録する設定を追加</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>診断の開始数・結果表示数・予約タップ率</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>20分</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>公開と同時</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>9/8</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>公開と同時（9/8）</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>登録前のデータはさかのぼって見られないため、公開と同時に設定します</t>
         </is>
@@ -1252,72 +1271,72 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>作業</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>（後片付け）</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>公開・計測</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>確認用ページを削除する</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>管理画面に確認用のページを残さない</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>公開と表示確認が終わったら削除</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>5分</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>公開後</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>9/12</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>公開後（目標 9/12）</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>下書きのため、一般の方には表示されていません</t>
         </is>
@@ -1327,72 +1346,72 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>作業</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>（計測）</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>公開・計測</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>メールマガジンのリンクに計測用の印を付ける</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>配信からの訪問と購入の動きを正しく計測する</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>配信システムのリンクに、どの配信から来たかが分かる印を付けます</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>配信からの訪問数・予約クリック数が正確に分かる</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>各配信前30分</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>9/16</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>各配信前</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>各配信の前（9/16〜）</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>9/17以降の全配信</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>現在は配信システムのドメインからの参照として集計され、効果を正確に測れていません（週11件）</t>
         </is>
@@ -1402,72 +1421,72 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>トップページの情報整理(写真・動画→コンセプト→今年の見どころ→チケット導線)</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>トップページの情報整理（写真・動画 → コンセプト → 今年の見どころ → チケット）</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>詰め込みすぎを解消し、最初の画面で魅力が伝わる構成にする</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>提案書を作成済み。写真・動画 → コンセプトと特徴 → 第8回の見どころ → チケット → お知らせ3件 … の順に再構成します</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>ヒーロー写真・動画、キャッチコピー、今年の見どころ3点(写真つき)</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>トップページのスクロール到達率（現状51%）、トップ→チケットページ遷移率、すぐ戻る割合</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>3日</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>素材到着後</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>9/26</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>素材が届き次第（目標 9/26 公開）</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>10/8 第3回配信前</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>提案済み（素材待ち）</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>トップページは28日間で3,782回閲覧、入口の73%。閲覧の65%が1ページだけで終了。現在お知らせ6件のうち2件が重複、1件は昨年の情報</t>
         </is>
@@ -1477,72 +1496,72 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>「東京から約60分、紅葉・秋川渓谷・花火の秋の日帰り旅」の体験価値とモデルコース</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>都心の花火大会との差別化。昼:観光・紅葉→夕方:会場イベント→夜:音楽×花火という目的の複数化で来場動機を作る</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>トップまたは専用ページに「秋川で過ごす一日」セクションを作成。既存の周辺観光ページ(18スポット)と相互リンク</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>モデルコースに載せる観光スポットの選定、所要時間の目安、写真</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>該当箇所の閲覧数、「秋川 紅葉」「サマーランド 花火」等の検索表示回数とクリック率、平均滞在時間</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>9/29</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>10/3</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>9/29 着手 → 10/3 公開</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>10/8 第3回配信「体験価値」に本文リンク</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="O16" s="6" t="inlineStr">
         <is>
           <t>検索「サマーランド 花火」は表示63回・クリック22回、「あきる野 花火」は表示43回・クリック11回で、地域名の検索に伸びしろがあります。周辺観光ページに18スポットの素材あり</t>
         </is>
@@ -1552,72 +1571,72 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>知る・行きたくなる</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>飲食・ステージのアピール(食べる/見る/楽しむ/感動する)</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>飲食・ステージのアピール（食べる／見る／楽しむ／感動する）</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>「花火直前に行くイベント」から「昼から楽しむイベント」へ認識を変える</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>4つの体験(キッチンカー・飲食ブース/ダンス・ステージ/秋川の自然・紅葉/音楽×花火)をカード形式で掲載</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>出店者・ステージ出演者の確定リスト、昨年の飲食・ステージ写真</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>該当箇所の閲覧数、出店者募集ページとの回遊</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>9/29</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>10/3</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>9/29 着手 → 10/3 公開</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>10/8 第3回配信</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>出店者募集ページは28日間で372回閲覧（前月比+75%）と関心が高い項目です</t>
         </is>
@@ -1627,72 +1646,72 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>知る</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>知る・行きたくなる</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>SNS・メディア出演情報のまとめ「秋川流域花火大会をもっと知る」</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>購入前に雰囲気を知れる場所を作り、点在する情報を一箇所に集める</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Instagram埋め込み・メディア掲載一覧・過去の動画をまとめる。既存のメディア掲載ページを第8回向けに更新</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>掲載するInstagram投稿の選定、メディア掲載一覧(媒体名・日付・リンク)</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>ページ閲覧数、SNSへのクリック数</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>低〜中</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>1日</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>10/6</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>10/6 着手 → 10/10 公開</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>10/22 第4回配信</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="O18" s="6" t="inlineStr">
         <is>
           <t>SNSからの訪問はInstagram週11件、X週5件と少なく、サイトからSNSへの案内も弱い状態です</t>
         </is>
@@ -1702,72 +1721,72 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>行きたくなる</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>知る・行きたくなる</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>当日タイムスケジュールの掲載</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>「何時に行けばどう楽しめるか」を示し、昼からの来場を促す</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>開場〜終了までの時間軸を図で掲載(トップ・チケット・初めての方へページから参照)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>開場時刻、ステージ進行、飲食開始時刻、花火打上時刻、終了時刻の確定</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>閲覧数、当日ガイドの利用数</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>中（確定後は高）</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>0.5日</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>プログラム確定後（目標10/10）</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>10/17</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>プログラム確定後に着手 → 10/17 公開</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>10/22 第4回配信</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>現在サイトに掲載している時間は第7回の記録です（飲食12:00〜20:00、パフォーマンス13:30〜17:30頃）。第8回のプログラム確定が前提となります</t>
         </is>
@@ -1777,72 +1796,72 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>⑧</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>安心して当日を迎える</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>「初めて来る人へ」ページ(行く前/会場内/帰り)</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>「初めて来る人へ」ページ（行く前／会場内／帰り）</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>アクセス・FAQに分散した情報を来場の時系列でまとめ、不安をなくす</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>到着推奨時刻、秋川駅からの行き方、電車/バス/車の比較、駐車場、会場マップ、帰りのバス時刻・注意点を1ページに構成</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>会場マップ最新版、トイレ・救護所・飲食ブースの位置、帰りのバス時刻、到着推奨時刻</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>ページ閲覧数、よくある質問・交通アクセスページとの回遊、お問い合わせ件数の減少</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>10/13</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>10/17</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>10/13 着手 → 10/17 公開</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>10/22 第4回配信「購入前確認」に本文リンク</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>交通アクセス296回・よくある質問313回の閲覧（28日間）。アクセスページの帰りの案内は現在「確定次第公開」のままです</t>
         </is>
@@ -1852,72 +1871,72 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>⑩</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>安心して当日を迎える</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>天候・開催情報(開催/中止判断、雨天対応、服装・防寒、当日の天気)</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>天候・開催情報（開催・中止の判断、雨天対応、服装・防寒）</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>当日の判断と準備の情報を一箇所で示し、電話問い合わせを減らす</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>トップ最上部に「開催情報」帯を用意(通常時は非表示)、専用ページに雨天時の対応・払い戻し・服装目安を掲載</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>中止判断のタイミングと告知ルール、荒天時の払い戻し方針、当日の更新担当者</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>当日週のトップページ閲覧数、開催情報ページ閲覧数、お問い合わせ件数</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>1日＋当日運用</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>10/20</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>10/24</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>10/20 着手 → 10/24 公開</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>10/31 第5回配信、11/13〜14 当日運用</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>よくある質問には「基本的に雨天決行」「11月は最高16℃・最低6℃」の記載があります。中止判断の基準と告知方法は未掲載、払い戻しは「イベント中止の場合のみ」となっています</t>
         </is>
@@ -1927,72 +1946,72 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>改善案</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>⑨</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>安心して当日を迎える</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>当日ガイドPDF(会場MAP・タイムスケジュール・バス時刻表)</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>当日ガイド（会場マップ・タイムスケジュール・バス時刻表）</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>会場で電波がつながりにくくても困らないよう、事前に保存・印刷できる資料を配る</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>A4×1〜2枚のPDFを作成し、⑧ページ・購入完了後の案内・最終メルマガからダウンロードできるようにする</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>最終版の会場マップ、確定タイムスケジュール、バス時刻表</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>ダウンロード数（現状は週6件）</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>10/20</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>10/30</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>10/20 着手 → 10/30 公開</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>10/31 第5回配信に添付・リンク</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N22" s="6" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O22" s="6" t="inlineStr">
         <is>
           <t>④⑧⑩の内容を流用して作成するため、それらの確定が前提</t>
         </is>
@@ -2031,7 +2050,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>週別スケジュール（✔=制作完了　■=作業　★=公開　◆=節目）　※2026年9月6日時点。No.は「計画表」シートと同じ通し番号です</t>
         </is>
@@ -2105,568 +2124,568 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>節目（メールマガジン・大会）</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr"/>
-      <c r="D4" s="12" t="inlineStr"/>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr"/>
+      <c r="D4" s="15" t="inlineStr"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>9/17 第2回配信</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="12" t="inlineStr"/>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr"/>
+      <c r="G4" s="15" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>10/8 第3回配信</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr"/>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>10/22 第4回配信</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>10/31 第5回配信・販売最終</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr"/>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="L4" s="15" t="inlineStr"/>
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>11/14 大会当日</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>旧URLの転送設定</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr"/>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr"/>
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr"/>
-      <c r="F5" s="14" t="inlineStr"/>
-      <c r="G5" s="14" t="inlineStr"/>
-      <c r="H5" s="14" t="inlineStr"/>
-      <c r="I5" s="14" t="inlineStr"/>
-      <c r="J5" s="14" t="inlineStr"/>
-      <c r="K5" s="14" t="inlineStr"/>
-      <c r="L5" s="14" t="inlineStr"/>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr"/>
+      <c r="F5" s="17" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr"/>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="17" t="inlineStr"/>
+      <c r="J5" s="17" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="17" t="inlineStr"/>
+      <c r="M5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>写真をタップで拡大</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr"/>
-      <c r="F6" s="14" t="inlineStr"/>
-      <c r="G6" s="14" t="inlineStr"/>
-      <c r="H6" s="14" t="inlineStr"/>
-      <c r="I6" s="14" t="inlineStr"/>
-      <c r="J6" s="14" t="inlineStr"/>
-      <c r="K6" s="14" t="inlineStr"/>
-      <c r="L6" s="14" t="inlineStr"/>
-      <c r="M6" s="14" t="inlineStr"/>
+      <c r="E6" s="17" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr"/>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="17" t="inlineStr"/>
+      <c r="J6" s="17" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="17" t="inlineStr"/>
+      <c r="M6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>SS・S・A席に予約ボタン</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr"/>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr"/>
-      <c r="I7" s="14" t="inlineStr"/>
-      <c r="J7" s="14" t="inlineStr"/>
-      <c r="K7" s="14" t="inlineStr"/>
-      <c r="L7" s="14" t="inlineStr"/>
-      <c r="M7" s="14" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="17" t="inlineStr"/>
+      <c r="J7" s="17" t="inlineStr"/>
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="17" t="inlineStr"/>
+      <c r="M7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>読み上げ・検索対応</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr"/>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr"/>
-      <c r="I8" s="14" t="inlineStr"/>
-      <c r="J8" s="14" t="inlineStr"/>
-      <c r="K8" s="14" t="inlineStr"/>
-      <c r="L8" s="14" t="inlineStr"/>
-      <c r="M8" s="14" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="17" t="inlineStr"/>
+      <c r="J8" s="17" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="17" t="inlineStr"/>
+      <c r="M8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>チケット入手方法の整理</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="14" t="inlineStr"/>
-      <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr"/>
-      <c r="J9" s="14" t="inlineStr"/>
-      <c r="K9" s="14" t="inlineStr"/>
-      <c r="L9" s="14" t="inlineStr"/>
-      <c r="M9" s="14" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr"/>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr"/>
+      <c r="H9" s="17" t="inlineStr"/>
+      <c r="I9" s="17" t="inlineStr"/>
+      <c r="J9" s="17" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="17" t="inlineStr"/>
+      <c r="M9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>座席診断</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
-      <c r="G10" s="14" t="inlineStr"/>
-      <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr"/>
-      <c r="J10" s="14" t="inlineStr"/>
-      <c r="K10" s="14" t="inlineStr"/>
-      <c r="L10" s="14" t="inlineStr"/>
-      <c r="M10" s="14" t="inlineStr"/>
+      <c r="E10" s="17" t="inlineStr"/>
+      <c r="F10" s="17" t="inlineStr"/>
+      <c r="G10" s="17" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="17" t="inlineStr"/>
+      <c r="J10" s="17" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="17" t="inlineStr"/>
+      <c r="M10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>チケットページの公開</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr"/>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-      <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
-      <c r="J11" s="14" t="inlineStr"/>
-      <c r="K11" s="14" t="inlineStr"/>
-      <c r="L11" s="14" t="inlineStr"/>
-      <c r="M11" s="14" t="inlineStr"/>
+      <c r="E11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="inlineStr"/>
+      <c r="G11" s="17" t="inlineStr"/>
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="17" t="inlineStr"/>
+      <c r="J11" s="17" t="inlineStr"/>
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="17" t="inlineStr"/>
+      <c r="M11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>アクセス解析の設定</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
-      <c r="G12" s="14" t="inlineStr"/>
-      <c r="H12" s="14" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr"/>
-      <c r="J12" s="14" t="inlineStr"/>
-      <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="14" t="inlineStr"/>
-      <c r="M12" s="14" t="inlineStr"/>
+      <c r="E12" s="17" t="inlineStr"/>
+      <c r="F12" s="17" t="inlineStr"/>
+      <c r="G12" s="17" t="inlineStr"/>
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr"/>
+      <c r="J12" s="17" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="17" t="inlineStr"/>
+      <c r="M12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>確認用ページの削除</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr"/>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr"/>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr"/>
-      <c r="J13" s="14" t="inlineStr"/>
-      <c r="K13" s="14" t="inlineStr"/>
-      <c r="L13" s="14" t="inlineStr"/>
-      <c r="M13" s="14" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="17" t="inlineStr"/>
+      <c r="M13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>配信リンクの計測設定</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="17" t="inlineStr"/>
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr"/>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr"/>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr"/>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr"/>
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr"/>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr"/>
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr"/>
-      <c r="M14" s="14" t="inlineStr"/>
+      <c r="L14" s="17" t="inlineStr"/>
+      <c r="M14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>トップページの情報整理</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr"/>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr"/>
+      <c r="D15" s="17" t="inlineStr"/>
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>(素材待ち)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr"/>
-      <c r="I15" s="14" t="inlineStr"/>
-      <c r="J15" s="14" t="inlineStr"/>
-      <c r="K15" s="14" t="inlineStr"/>
-      <c r="L15" s="14" t="inlineStr"/>
-      <c r="M15" s="14" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr"/>
+      <c r="I15" s="17" t="inlineStr"/>
+      <c r="J15" s="17" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="17" t="inlineStr"/>
+      <c r="M15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>体験価値・モデルコース</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr"/>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr"/>
+      <c r="D16" s="17" t="inlineStr"/>
+      <c r="E16" s="17" t="inlineStr"/>
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="14" t="inlineStr"/>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="14" t="inlineStr"/>
-      <c r="M16" s="14" t="inlineStr"/>
+      <c r="I16" s="17" t="inlineStr"/>
+      <c r="J16" s="17" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="17" t="inlineStr"/>
+      <c r="M16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>飲食・ステージのアピール</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr"/>
+      <c r="D17" s="17" t="inlineStr"/>
+      <c r="E17" s="17" t="inlineStr"/>
+      <c r="F17" s="17" t="inlineStr"/>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr"/>
-      <c r="L17" s="14" t="inlineStr"/>
-      <c r="M17" s="14" t="inlineStr"/>
+      <c r="I17" s="17" t="inlineStr"/>
+      <c r="J17" s="17" t="inlineStr"/>
+      <c r="K17" s="17" t="inlineStr"/>
+      <c r="L17" s="17" t="inlineStr"/>
+      <c r="M17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>SNS・メディアまとめ</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr"/>
-      <c r="D18" s="14" t="inlineStr"/>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="14" t="inlineStr"/>
-      <c r="G18" s="14" t="inlineStr"/>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr"/>
+      <c r="D18" s="17" t="inlineStr"/>
+      <c r="E18" s="17" t="inlineStr"/>
+      <c r="F18" s="17" t="inlineStr"/>
+      <c r="G18" s="17" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr"/>
-      <c r="J18" s="14" t="inlineStr"/>
-      <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="14" t="inlineStr"/>
-      <c r="M18" s="14" t="inlineStr"/>
+      <c r="I18" s="17" t="inlineStr"/>
+      <c r="J18" s="17" t="inlineStr"/>
+      <c r="K18" s="17" t="inlineStr"/>
+      <c r="L18" s="17" t="inlineStr"/>
+      <c r="M18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>当日タイムスケジュール</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="14" t="inlineStr"/>
-      <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="14" t="inlineStr"/>
-      <c r="G19" s="14" t="inlineStr"/>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr"/>
+      <c r="D19" s="17" t="inlineStr"/>
+      <c r="E19" s="17" t="inlineStr"/>
+      <c r="F19" s="17" t="inlineStr"/>
+      <c r="G19" s="17" t="inlineStr"/>
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>(確定待ち)</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr"/>
-      <c r="K19" s="14" t="inlineStr"/>
-      <c r="L19" s="14" t="inlineStr"/>
-      <c r="M19" s="14" t="inlineStr"/>
+      <c r="J19" s="17" t="inlineStr"/>
+      <c r="K19" s="17" t="inlineStr"/>
+      <c r="L19" s="17" t="inlineStr"/>
+      <c r="M19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>初めて来る人へ</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="14" t="inlineStr"/>
-      <c r="F20" s="14" t="inlineStr"/>
-      <c r="G20" s="14" t="inlineStr"/>
-      <c r="H20" s="14" t="inlineStr"/>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr"/>
+      <c r="D20" s="17" t="inlineStr"/>
+      <c r="E20" s="17" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr"/>
+      <c r="G20" s="17" t="inlineStr"/>
+      <c r="H20" s="17" t="inlineStr"/>
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr"/>
-      <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="14" t="inlineStr"/>
-      <c r="M20" s="14" t="inlineStr"/>
+      <c r="J20" s="17" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr"/>
+      <c r="L20" s="17" t="inlineStr"/>
+      <c r="M20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>天候・開催情報</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr"/>
-      <c r="E21" s="14" t="inlineStr"/>
-      <c r="F21" s="14" t="inlineStr"/>
-      <c r="G21" s="14" t="inlineStr"/>
-      <c r="H21" s="14" t="inlineStr"/>
-      <c r="I21" s="14" t="inlineStr"/>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr"/>
+      <c r="D21" s="17" t="inlineStr"/>
+      <c r="E21" s="17" t="inlineStr"/>
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr"/>
+      <c r="I21" s="17" t="inlineStr"/>
+      <c r="J21" s="18" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr"/>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="K21" s="17" t="inlineStr"/>
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="M21" s="17" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>当日ガイド</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="14" t="inlineStr"/>
-      <c r="E22" s="14" t="inlineStr"/>
-      <c r="F22" s="14" t="inlineStr"/>
-      <c r="G22" s="14" t="inlineStr"/>
-      <c r="H22" s="14" t="inlineStr"/>
-      <c r="I22" s="14" t="inlineStr"/>
-      <c r="J22" s="17" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr"/>
+      <c r="D22" s="17" t="inlineStr"/>
+      <c r="E22" s="17" t="inlineStr"/>
+      <c r="F22" s="17" t="inlineStr"/>
+      <c r="G22" s="17" t="inlineStr"/>
+      <c r="H22" s="17" t="inlineStr"/>
+      <c r="I22" s="17" t="inlineStr"/>
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="K22" s="18" t="inlineStr">
         <is>
           <t>■★</t>
         </is>
       </c>
-      <c r="L22" s="14" t="inlineStr"/>
-      <c r="M22" s="17" t="inlineStr">
+      <c r="L22" s="17" t="inlineStr"/>
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>※ 9/1週の「✔」は制作と点検が完了したもの、9/8週の「★」は公開の予定です。</t>
         </is>
@@ -2694,7 +2713,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>実行委員会でご用意・ご判断いただきたいこと（期限順）　※2026年9月6日更新</t>
         </is>
@@ -2735,487 +2754,487 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>9/8</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>チケットページを公開してよいかのご判断</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>No.7 チケットページの公開</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>確認用ページでご覧いただけます。ご判断後すぐに公開できます</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>座席診断のおすすめ振り分け(全20通り)の確認。特に「カップル×花火に集中＝S席」「おひとり×ゆったり＝A席」「おひとり×特別な時間＝S席」</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>No.6 座席診断</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>初期案として設定済み。結果に「※おすすめは目安です」を表示</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>A席「子ども2,000円」の年齢区分(何歳から席が必要か)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>No.6 座席診断</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>年齢は書かず「小さなお子さまの膝上観覧は無料です」のみ</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>フリーエリア「西多摩在住」の確認方法(全員が在住である必要があるか、証明は必要か)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>No.6 座席診断</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>「西多摩にお住まいの方だけが買える」までにとどめている</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>5名以上の家族・グループへの案内(SS席を2テーブル買えるか、隣同士になるか)</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>No.6 座席診断</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>サイトに記載がないため書いていない</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>1人あたり換算(SS席8,750円/S席7,000円)と差額(A席→S席 あと4,000円)の表示可否</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>No.6 座席診断</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>表示価格の割り算・引き算のみで「〜の計算です」と記載</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>写真の説明文(alt)の言い回し 例:「SS席(4名掛けのテーブル席)の写真」</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>No.4 読み上げ・検索への対応</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>実際の画像を見て、席名と写っているものだけで記載</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>寄付・協賛カードの金額表記「寄付1万円から/中口協賛3万円から/大口協賛10万円以上」</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>No.5 チケット入手方法の整理</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>寄付・協賛ページの記載どおり。特典の中身は書いていない</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>ふるさと納税の受付期限、返礼品ページのURLに変更がないか</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>No.5 チケット入手方法の整理</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>現在のさとふるの返礼品一覧へリンク</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>トップページ用の写真・動画（横・縦）、キャッチコピー、今年の見どころ3点（写真つき）</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>No.11 トップページの整理</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>―（素材がそろってからの着手となります）</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>席種ごとの配置が分かる図。いただければ「花火の見え方」を説明に加えられます</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>No.6 座席診断／No.16 初めて来る人へ</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>配置の情報がないため「指定席で場所取りが不要」という点を中心に説明</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>予約ボタンの色をサイト全体でそろえるか（座席診断は文字の読みやすさの基準を満たす少し暗い赤、既存ボタンは従来の赤）</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>No.3 予約ボタン／No.6 座席診断</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>座席診断のみ暗めの赤。ほかは従来どおり</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>モデルコースに載せる観光スポットの選定、所要時間の目安、写真</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>No.12 体験価値・モデルコース</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>周辺観光ページの18スポットから選べます</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>9/26</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>出店者・ステージ出演者の確定リスト、昨年の飲食・ステージ写真</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>No.13 飲食・ステージ</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>未確定分は「予定」表記で先行公開も可能</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>10/3</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>掲載するInstagram投稿の選定、メディア掲載一覧(媒体・日付・リンク)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>No.14 SNS・メディアまとめ</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>第8回の当日プログラム(開場・ステージ進行・飲食開始・打上・終了時刻)</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>No.15 タイムスケジュール／No.18 当日ガイド／No.6 座席診断</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>サイトの時間は第7回の記録のまま(飲食12:00〜20:00等)</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>会場マップ最新版(座席・トイレ・救護所・飲食・ステージ)、到着推奨時刻</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>No.16 初めて来る人へ／No.18 当日ガイド</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>帰りのバス時刻表(交通事業者へ確認)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>No.16 初めて来る人へ／No.18 当日ガイド</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>アクセスページは「確定次第、順次公開します」のまま</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>10/17</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>中止判断のタイミングと告知ルール、荒天時の払い戻し方針、当日の更新担当者</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>No.17 天候・開催情報</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>FAQは「基本的に雨天決行」「払い戻しはイベント中止の場合のみ」</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>10/24</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>会場マップ・タイムスケジュール・バス時刻表の最終版</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>No.18 当日ガイド</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>随時</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>S席の追加販売が終わったとき/フリーエリアが完売したときの連絡</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>No.6 座席診断</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>そのまま表示しています。ご連絡いただければ、おすすめする席を変更します</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3242,7 +3261,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>効果を測る指標　現状値（2026年8月29日〜9月4日）と目標</t>
         </is>
@@ -3276,459 +3295,459 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>週間の訪問者数 / 閲覧数</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>1,340人 / 3,930回（前週比 +101% / +110%）</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>配信のある週で2,000人以上</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>サイト内のアクセス集計</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>検索からのクリック数 / クリック率 / 平均掲載順位（週）</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>648回 / 14.4% / 5.6位</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>クリック率16%以上（地域名の検索の改善）</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>検索エンジンの管理ツール</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>No.11・12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>チケットページの閲覧数（28日間）</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>2,171回</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>3,000回</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>No.5・6</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>予約サイトへのクリック数（週）</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>316回（前週比 +185%）</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>配信のある週で400回以上</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>No.3・5・6</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>トップページを下まで読んだ割合</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>60%以上</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>No.11</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>開いてすぐ前のページに戻った割合</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>27%（411件）</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>20%以下</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>No.2・5・11</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>押しても反応しない箇所へのタップ</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>16.7%（253件）</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>10%以下</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>No.2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>初めて訪れた方の割合</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>77.7%</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>―（参考値）</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>メールマガジン経由の訪問（週）</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>11件（正確に計測できていない状態）</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>計測を整えたうえで、開封数の20%以上</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>No.10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>資料のダウンロード数（週）</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>6件</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>大会前週に300件以上</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>No.18</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>「ページが見つかりません」の発生</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>旧URLで発生中</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>0件</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>サイト内のアクセス集計</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>No.1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>チケット販売（累計・9月4日時点）</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>882席 / 5,518,000円（目標比 20.5%）</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>26,860,000円</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>売上集計シート</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>【新】座席診断を始めた数（週）</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>未計測（公開後に取得）</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>公開後1週間の実測をもとに設定</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>【新】診断結果まで進んだ数（週）</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>始めた数の80%以上（途中でやめる方が少ない）</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>【新】診断結果から予約ボタンを押した割合</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>30%以上</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>【新】診断でおすすめされた席の内訳</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>A席の予約が増えているか（現状A席は目標比6.8%）</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>アクセス解析</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>【新】写真の拡大表示の利用</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>未計測</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>反応しない箇所へのタップの減少で確認</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>行動分析ツール</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>No.2</t>
         </is>
@@ -3753,7 +3772,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>チケットページ公開までの手順と補足（2026年9月6日）</t>
         </is>
@@ -3772,132 +3791,132 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>確認用ページ</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>https://machizukuri-con.or.jp/?page_id=4524&amp;preview=true　（公開前の下書きです。サイト管理画面にログインできる方のみ閲覧できます。スマートフォンでもご確認いただけます）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>手順①　ご判断</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>確認用ページをご覧いただき、この内容で公開してよいかご判断ください</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>手順②　公開</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>チケットページ（固定ページ「チケット情報」）の内容を、確認用ページと同じ内容に差し替えます</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>手順③　表示確認</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>公開後、https://machizukuri-con.or.jp/ticket/ をスマートフォンの実機で開いて確認します。確認する点：上から「チケットの入手方法は3つ」→「どの席にしようか迷ったら」→「販売サイト」の順に並ぶ／座席診断が動く／写真をタップすると拡大する／横にはみ出さない</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>手順④　計測設定</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>アクセス解析（GA4）に座席診断の項目を登録します。登録前のデータはさかのぼって見られないため、公開と同時に行います</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>手順⑤　後片付け</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>確認用の下書きページを削除します</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>元に戻す方法</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>サイトの変更履歴から、いつでも公開前の状態に戻せます。公開前の内容も別途保管しています</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>変更していないもの</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>既存の文言・価格・掲載していない項目は一切変更していません（変更部分以外が元の内容と完全に一致することを機械的に確認済みです）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>座席診断の仕組みについて</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>利用しているレンタルサーバーのセキュリティ機能により、ページ本文の中にプログラムを直接書き込むことができません。そのため座席診断のプログラムは、当会が管理する別の配信先から読み込む形にしています（表示・動作に違いはありません）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>確認した内容</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>複数の案を比較したうえで制作し、事実関係・日本語表現・スマートフォン表示・動作・サイトへの組み込み・読み上げ対応の6つの観点で点検しました。パソコンとスマートフォンの表示、座席診断の全20通り、写真の拡大表示、編集画面でエラーが出ないことを実機で確認しています</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>関連資料</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>「チケットページ改善のまとめ」「トップページ整理の提案書」「座席診断の仕様書」を別途作成しています（ご入用の場合はお知らせください）</t>
         </is>
